--- a/data/fig7/mainFigData.xlsx
+++ b/data/fig7/mainFigData.xlsx
@@ -25,15 +25,15 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="340">
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geoSample</t>
+  </si>
+  <si>
     <t xml:space="preserve">Treatment</t>
   </si>
   <si>
-    <t xml:space="preserve">geoSample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
     <t xml:space="preserve">Clonality</t>
   </si>
   <si>
@@ -43,15 +43,15 @@
     <t xml:space="preserve">N</t>
   </si>
   <si>
+    <t xml:space="preserve">d80 WTNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT3</t>
+  </si>
+  <si>
     <t xml:space="preserve">WTNT</t>
   </si>
   <si>
-    <t xml:space="preserve">APT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d80 WTNT</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT4</t>
   </si>
   <si>
@@ -73,24 +73,24 @@
     <t xml:space="preserve">APT10</t>
   </si>
   <si>
+    <t xml:space="preserve">d80 Untreated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Untreated</t>
   </si>
   <si>
-    <t xml:space="preserve">APT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d80 Untreated</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT2</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 WTNT</t>
+  </si>
+  <si>
     <t xml:space="preserve">APT134</t>
   </si>
   <si>
-    <t xml:space="preserve">d105 WTNT</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT135</t>
   </si>
   <si>
@@ -103,12 +103,12 @@
     <t xml:space="preserve">APT138</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 Untreated</t>
+  </si>
+  <si>
     <t xml:space="preserve">APT19</t>
   </si>
   <si>
-    <t xml:space="preserve">d105 Untreated</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT20</t>
   </si>
   <si>
@@ -142,15 +142,15 @@
     <t xml:space="preserve">APT30</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PTX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT43</t>
+  </si>
+  <si>
     <t xml:space="preserve">PTX</t>
   </si>
   <si>
-    <t xml:space="preserve">APT43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PTX</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT44</t>
   </si>
   <si>
@@ -199,15 +199,15 @@
     <t xml:space="preserve">APT133</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT107</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLX</t>
   </si>
   <si>
-    <t xml:space="preserve">APT107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PLX</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT108</t>
   </si>
   <si>
@@ -238,15 +238,15 @@
     <t xml:space="preserve">APT117</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX+PTX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT54</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLX+PTX</t>
   </si>
   <si>
-    <t xml:space="preserve">APT54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PLX+PTX</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT55</t>
   </si>
   <si>
@@ -304,15 +304,15 @@
     <t xml:space="preserve">APT131</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PTX+aPD-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT94</t>
+  </si>
+  <si>
     <t xml:space="preserve">PTX+aPD-1</t>
   </si>
   <si>
-    <t xml:space="preserve">APT94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PTX+aPD-1</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT95</t>
   </si>
   <si>
@@ -337,15 +337,15 @@
     <t xml:space="preserve">APT102</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX+PTX+aPD-1_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT81</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLX+PTX+aPD-1_R</t>
   </si>
   <si>
-    <t xml:space="preserve">APT81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PLX+PTX+aPD-1_R</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT82</t>
   </si>
   <si>
@@ -370,15 +370,15 @@
     <t xml:space="preserve">APT125</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX+PTX+aPD-1_NR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT84</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLX+PTX+aPD-1_NR</t>
   </si>
   <si>
-    <t xml:space="preserve">APT84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PLX+PTX+aPD-1_NR</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT85</t>
   </si>
   <si>
@@ -400,15 +400,15 @@
     <t xml:space="preserve">APT127</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 aPD-L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT11</t>
+  </si>
+  <si>
     <t xml:space="preserve">aPD-L1</t>
   </si>
   <si>
-    <t xml:space="preserve">APT11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 aPD-L1</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT12</t>
   </si>
   <si>
@@ -430,15 +430,15 @@
     <t xml:space="preserve">APT18</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PTX+aPD-L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT31</t>
+  </si>
+  <si>
     <t xml:space="preserve">PTX+aPD-L1</t>
   </si>
   <si>
-    <t xml:space="preserve">APT31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PTX+aPD-L1</t>
-  </si>
-  <si>
     <t xml:space="preserve">APT32</t>
   </si>
   <si>
@@ -472,13 +472,13 @@
     <t xml:space="preserve">APT42</t>
   </si>
   <si>
+    <t xml:space="preserve">d105 PLX+PTX+aPD-L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APT64</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLX+PTX+aPD-L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APT64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d105 PLX+PTX+aPD-L1</t>
   </si>
   <si>
     <t xml:space="preserve">APT65</t>
@@ -1408,7 +1408,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1428,7 +1428,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1448,7 +1448,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1468,7 +1468,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1488,7 +1488,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1508,7 +1508,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1528,7 +1528,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1548,7 +1548,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1568,7 +1568,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1588,18 +1588,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>0.155536146654218</v>
@@ -1608,18 +1608,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>0.178406000612276</v>
@@ -1628,18 +1628,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>0.114817920937953</v>
@@ -1648,18 +1648,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>0.115306282145325</v>
@@ -1668,18 +1668,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0.211761384819304</v>
@@ -1688,18 +1688,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
         <v>0.117921822696709</v>
@@ -1708,18 +1708,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
         <v>0.117745913759565</v>
@@ -1728,18 +1728,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
         <v>0.118054839018281</v>
@@ -1748,18 +1748,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
         <v>0.13582098567486</v>
@@ -1768,18 +1768,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D21" t="n">
         <v>0.129739543928145</v>
@@ -1788,18 +1788,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
         <v>0.142647803222944</v>
@@ -1808,18 +1808,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
         <v>0.111680364933223</v>
@@ -1828,18 +1828,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D24" t="n">
         <v>0.114645932518392</v>
@@ -1848,18 +1848,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D25" t="n">
         <v>0.100100766008985</v>
@@ -1868,18 +1868,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
         <v>0.0966225694258327</v>
@@ -1888,18 +1888,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
         <v>0.166684851899832</v>
@@ -1908,18 +1908,18 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
         <v>0.148588929161918</v>
@@ -1928,7 +1928,7 @@
         <v>0.0629030175468878</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -7157,7 +7157,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -7177,7 +7177,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -7197,7 +7197,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -7217,7 +7217,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -7237,7 +7237,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -7257,7 +7257,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -7277,7 +7277,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -7317,7 +7317,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -7337,18 +7337,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>8.63159918275365</v>
@@ -7357,18 +7357,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>7.99827419261466</v>
@@ -7377,18 +7377,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>8.7287320880808</v>
@@ -7397,18 +7397,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>8.63324983312079</v>
@@ -7417,18 +7417,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>6.87765380058593</v>
@@ -7437,18 +7437,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
         <v>5.10449589439713</v>
@@ -7457,18 +7457,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
         <v>5.86609378860888</v>
@@ -7477,18 +7477,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
         <v>5.61336113086027</v>
@@ -7497,18 +7497,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
         <v>4.82188542122136</v>
@@ -7517,18 +7517,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D21" t="n">
         <v>5.59271877592764</v>
@@ -7537,18 +7537,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
         <v>5.78304320201087</v>
@@ -7557,18 +7557,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
         <v>5.00866116223961</v>
@@ -7577,18 +7577,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D24" t="n">
         <v>6.17736441577631</v>
@@ -7597,18 +7597,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D25" t="n">
         <v>6.05938320461809</v>
@@ -7617,18 +7617,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
         <v>6.48631307439064</v>
@@ -7637,18 +7637,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
         <v>5.34579747260902</v>
@@ -7657,18 +7657,18 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
         <v>5.18620866950636</v>
@@ -7677,7 +7677,7 @@
         <v>2.39697887132633</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -9916,10 +9916,10 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D1" t="s">
         <v>169</v>
@@ -9942,10 +9942,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>0.0959530675151636</v>
@@ -9968,10 +9968,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>0.0554845056566651</v>
@@ -9994,10 +9994,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>0.0820466242809567</v>
@@ -10020,10 +10020,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>0.0505311228035342</v>
@@ -10046,10 +10046,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>0.0462850182704019</v>
@@ -10072,10 +10072,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>0.0444553483807655</v>
@@ -10098,10 +10098,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>0.109411764705882</v>
@@ -10124,10 +10124,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>0.0806356680400236</v>
@@ -10150,10 +10150,10 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
       </c>
       <c r="D10" t="n">
         <v>0.142616951834636</v>
@@ -10176,10 +10176,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
         <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
       </c>
       <c r="D11" t="n">
         <v>0.11727842435094</v>
@@ -10199,13 +10199,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
         <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>0.0248637149315251</v>
@@ -10228,10 +10228,10 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
         <v>0.135623869801085</v>
@@ -10254,10 +10254,10 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
         <v>0.0256605414809177</v>
@@ -10280,10 +10280,10 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
         <v>0.0426545086119554</v>
@@ -10306,10 +10306,10 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>0.223932820153954</v>
@@ -10329,13 +10329,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
         <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
       </c>
       <c r="D17" t="n">
         <v>0.110094480358031</v>
@@ -10358,10 +10358,10 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>0.0966531740546944</v>
@@ -10384,10 +10384,10 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
         <v>0.0942910853863659</v>
@@ -10410,10 +10410,10 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
         <v>0.142545382402539</v>
@@ -10436,10 +10436,10 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
         <v>0.146157659890927</v>
@@ -10462,10 +10462,10 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
         <v>0.139571611884315</v>
@@ -10488,10 +10488,10 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
         <v>0.151256331313934</v>
@@ -10514,10 +10514,10 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" t="n">
         <v>0.0964437001280661</v>
@@ -10540,10 +10540,10 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" t="n">
         <v>0.0652975775097198</v>
@@ -10566,10 +10566,10 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
         <v>0.0598290598290598</v>
@@ -10592,10 +10592,10 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
         <v>0.203690842345471</v>
@@ -10618,10 +10618,10 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" t="n">
         <v>0.136794807788318</v>
@@ -10644,10 +10644,10 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
         <v>39</v>
-      </c>
-      <c r="C29" t="s">
-        <v>41</v>
       </c>
       <c r="D29" t="n">
         <v>0.16077424451906</v>
@@ -10670,10 +10670,10 @@
         <v>42</v>
       </c>
       <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s">
         <v>39</v>
-      </c>
-      <c r="C30" t="s">
-        <v>41</v>
       </c>
       <c r="D30" t="n">
         <v>0.0746505402993953</v>
@@ -10696,10 +10696,10 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s">
         <v>39</v>
-      </c>
-      <c r="C31" t="s">
-        <v>41</v>
       </c>
       <c r="D31" t="n">
         <v>0.00726573351853832</v>
@@ -10722,10 +10722,10 @@
         <v>44</v>
       </c>
       <c r="B32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" t="s">
         <v>39</v>
-      </c>
-      <c r="C32" t="s">
-        <v>41</v>
       </c>
       <c r="D32" t="n">
         <v>0.120031639311845</v>
@@ -10748,10 +10748,10 @@
         <v>45</v>
       </c>
       <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" t="s">
         <v>39</v>
-      </c>
-      <c r="C33" t="s">
-        <v>41</v>
       </c>
       <c r="D33" t="n">
         <v>0.0916188970152205</v>
@@ -10774,10 +10774,10 @@
         <v>46</v>
       </c>
       <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
         <v>39</v>
-      </c>
-      <c r="C34" t="s">
-        <v>41</v>
       </c>
       <c r="D34" t="n">
         <v>0.105231807803038</v>
@@ -10800,10 +10800,10 @@
         <v>47</v>
       </c>
       <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s">
         <v>39</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
       </c>
       <c r="D35" t="n">
         <v>0.482411559541604</v>
@@ -10826,10 +10826,10 @@
         <v>48</v>
       </c>
       <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
         <v>39</v>
-      </c>
-      <c r="C36" t="s">
-        <v>41</v>
       </c>
       <c r="D36" t="n">
         <v>0.101642913697546</v>
@@ -10852,10 +10852,10 @@
         <v>49</v>
       </c>
       <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" t="s">
         <v>39</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
       </c>
       <c r="D37" t="n">
         <v>0.144199386806449</v>
@@ -10878,10 +10878,10 @@
         <v>50</v>
       </c>
       <c r="B38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s">
         <v>39</v>
-      </c>
-      <c r="C38" t="s">
-        <v>41</v>
       </c>
       <c r="D38" t="n">
         <v>0.102979145978153</v>
@@ -10904,10 +10904,10 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" t="s">
         <v>39</v>
-      </c>
-      <c r="C39" t="s">
-        <v>41</v>
       </c>
       <c r="D39" t="n">
         <v>0.141121128969032</v>
@@ -10930,10 +10930,10 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" t="s">
         <v>39</v>
-      </c>
-      <c r="C40" t="s">
-        <v>41</v>
       </c>
       <c r="D40" t="n">
         <v>0.204665012406948</v>
@@ -10956,10 +10956,10 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s">
         <v>39</v>
-      </c>
-      <c r="C41" t="s">
-        <v>41</v>
       </c>
       <c r="D41" t="n">
         <v>0.112070676990272</v>
@@ -10982,10 +10982,10 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s">
         <v>39</v>
-      </c>
-      <c r="C42" t="s">
-        <v>41</v>
       </c>
       <c r="D42" t="n">
         <v>0.184356986682568</v>
@@ -11008,10 +11008,10 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s">
         <v>39</v>
-      </c>
-      <c r="C43" t="s">
-        <v>41</v>
       </c>
       <c r="D43" t="n">
         <v>0.0988279698053238</v>
@@ -11034,10 +11034,10 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s">
         <v>39</v>
-      </c>
-      <c r="C44" t="s">
-        <v>41</v>
       </c>
       <c r="D44" t="n">
         <v>0.127325756813839</v>
@@ -11060,10 +11060,10 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" t="s">
         <v>39</v>
-      </c>
-      <c r="C45" t="s">
-        <v>41</v>
       </c>
       <c r="D45" t="n">
         <v>0.0837565979484115</v>
@@ -11086,10 +11086,10 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" t="s">
         <v>58</v>
-      </c>
-      <c r="C46" t="s">
-        <v>60</v>
       </c>
       <c r="D46" t="n">
         <v>0.130421865715983</v>
@@ -11112,10 +11112,10 @@
         <v>61</v>
       </c>
       <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="s">
         <v>58</v>
-      </c>
-      <c r="C47" t="s">
-        <v>60</v>
       </c>
       <c r="D47" t="n">
         <v>0.524665012406948</v>
@@ -11138,10 +11138,10 @@
         <v>62</v>
       </c>
       <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" t="s">
         <v>58</v>
-      </c>
-      <c r="C48" t="s">
-        <v>60</v>
       </c>
       <c r="D48" t="n">
         <v>0.0519951632406287</v>
@@ -11164,10 +11164,10 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" t="s">
         <v>58</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
       </c>
       <c r="D49" t="n">
         <v>0.181602138825626</v>
@@ -11190,10 +11190,10 @@
         <v>64</v>
       </c>
       <c r="B50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" t="s">
         <v>58</v>
-      </c>
-      <c r="C50" t="s">
-        <v>60</v>
       </c>
       <c r="D50" t="n">
         <v>0.119602977667494</v>
@@ -11216,10 +11216,10 @@
         <v>65</v>
       </c>
       <c r="B51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" t="s">
         <v>58</v>
-      </c>
-      <c r="C51" t="s">
-        <v>60</v>
       </c>
       <c r="D51" t="n">
         <v>0.171258671952428</v>
@@ -11242,10 +11242,10 @@
         <v>66</v>
       </c>
       <c r="B52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" t="s">
         <v>58</v>
-      </c>
-      <c r="C52" t="s">
-        <v>60</v>
       </c>
       <c r="D52" t="n">
         <v>0.148298779882948</v>
@@ -11268,10 +11268,10 @@
         <v>67</v>
       </c>
       <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" t="s">
         <v>58</v>
-      </c>
-      <c r="C53" t="s">
-        <v>60</v>
       </c>
       <c r="D53" t="n">
         <v>0.0840202602045883</v>
@@ -11294,10 +11294,10 @@
         <v>68</v>
       </c>
       <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" t="s">
         <v>58</v>
-      </c>
-      <c r="C54" t="s">
-        <v>60</v>
       </c>
       <c r="D54" t="n">
         <v>0.457465794170137</v>
@@ -11320,10 +11320,10 @@
         <v>69</v>
       </c>
       <c r="B55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" t="s">
         <v>58</v>
-      </c>
-      <c r="C55" t="s">
-        <v>60</v>
       </c>
       <c r="D55" t="n">
         <v>0.121851667496267</v>
@@ -11346,10 +11346,10 @@
         <v>70</v>
       </c>
       <c r="B56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" t="s">
         <v>58</v>
-      </c>
-      <c r="C56" t="s">
-        <v>60</v>
       </c>
       <c r="D56" t="n">
         <v>0.188262119559829</v>
@@ -11372,10 +11372,10 @@
         <v>72</v>
       </c>
       <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
         <v>71</v>
-      </c>
-      <c r="C57" t="s">
-        <v>73</v>
       </c>
       <c r="D57" t="n">
         <v>0.100049975012494</v>
@@ -11398,10 +11398,10 @@
         <v>74</v>
       </c>
       <c r="B58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" t="s">
         <v>71</v>
-      </c>
-      <c r="C58" t="s">
-        <v>73</v>
       </c>
       <c r="D58" t="n">
         <v>0.025949953660797</v>
@@ -11424,10 +11424,10 @@
         <v>75</v>
       </c>
       <c r="B59" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" t="s">
         <v>71</v>
-      </c>
-      <c r="C59" t="s">
-        <v>73</v>
       </c>
       <c r="D59" t="n">
         <v>0.0798914681941514</v>
@@ -11450,10 +11450,10 @@
         <v>76</v>
       </c>
       <c r="B60" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" t="s">
         <v>71</v>
-      </c>
-      <c r="C60" t="s">
-        <v>73</v>
       </c>
       <c r="D60" t="n">
         <v>0.0870037527157812</v>
@@ -11476,10 +11476,10 @@
         <v>77</v>
       </c>
       <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
         <v>71</v>
-      </c>
-      <c r="C61" t="s">
-        <v>73</v>
       </c>
       <c r="D61" t="n">
         <v>0.0674035330109543</v>
@@ -11502,10 +11502,10 @@
         <v>78</v>
       </c>
       <c r="B62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" t="s">
         <v>71</v>
-      </c>
-      <c r="C62" t="s">
-        <v>73</v>
       </c>
       <c r="D62" t="n">
         <v>0.135499207606973</v>
@@ -11528,10 +11528,10 @@
         <v>79</v>
       </c>
       <c r="B63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" t="s">
         <v>71</v>
-      </c>
-      <c r="C63" t="s">
-        <v>73</v>
       </c>
       <c r="D63" t="n">
         <v>0.130711796913887</v>
@@ -11554,10 +11554,10 @@
         <v>80</v>
       </c>
       <c r="B64" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" t="s">
         <v>71</v>
-      </c>
-      <c r="C64" t="s">
-        <v>73</v>
       </c>
       <c r="D64" t="n">
         <v>0.223424317617866</v>
@@ -11580,10 +11580,10 @@
         <v>81</v>
       </c>
       <c r="B65" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" t="s">
         <v>71</v>
-      </c>
-      <c r="C65" t="s">
-        <v>73</v>
       </c>
       <c r="D65" t="n">
         <v>0.186686390532544</v>
@@ -11606,10 +11606,10 @@
         <v>82</v>
       </c>
       <c r="B66" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" t="s">
         <v>71</v>
-      </c>
-      <c r="C66" t="s">
-        <v>73</v>
       </c>
       <c r="D66" t="n">
         <v>0.112088791120888</v>
@@ -11632,10 +11632,10 @@
         <v>83</v>
       </c>
       <c r="B67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" t="s">
         <v>71</v>
-      </c>
-      <c r="C67" t="s">
-        <v>73</v>
       </c>
       <c r="D67" t="n">
         <v>0.286409212746947</v>
@@ -11658,10 +11658,10 @@
         <v>84</v>
       </c>
       <c r="B68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" t="s">
         <v>71</v>
-      </c>
-      <c r="C68" t="s">
-        <v>73</v>
       </c>
       <c r="D68" t="n">
         <v>0.137295690936107</v>
@@ -11684,10 +11684,10 @@
         <v>85</v>
       </c>
       <c r="B69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" t="s">
         <v>71</v>
-      </c>
-      <c r="C69" t="s">
-        <v>73</v>
       </c>
       <c r="D69" t="n">
         <v>0.079457747872551</v>
@@ -11710,10 +11710,10 @@
         <v>86</v>
       </c>
       <c r="B70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" t="s">
         <v>71</v>
-      </c>
-      <c r="C70" t="s">
-        <v>73</v>
       </c>
       <c r="D70" t="n">
         <v>0.160457029309488</v>
@@ -11736,10 +11736,10 @@
         <v>87</v>
       </c>
       <c r="B71" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" t="s">
         <v>71</v>
-      </c>
-      <c r="C71" t="s">
-        <v>73</v>
       </c>
       <c r="D71" t="n">
         <v>0.219023034154091</v>
@@ -11762,10 +11762,10 @@
         <v>88</v>
       </c>
       <c r="B72" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" t="s">
         <v>71</v>
-      </c>
-      <c r="C72" t="s">
-        <v>73</v>
       </c>
       <c r="D72" t="n">
         <v>0.214901416823541</v>
@@ -11788,10 +11788,10 @@
         <v>89</v>
       </c>
       <c r="B73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" t="s">
         <v>71</v>
-      </c>
-      <c r="C73" t="s">
-        <v>73</v>
       </c>
       <c r="D73" t="n">
         <v>0.255987280135149</v>
@@ -11814,10 +11814,10 @@
         <v>90</v>
       </c>
       <c r="B74" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" t="s">
         <v>71</v>
-      </c>
-      <c r="C74" t="s">
-        <v>73</v>
       </c>
       <c r="D74" t="n">
         <v>0.20421974522293</v>
@@ -11840,10 +11840,10 @@
         <v>91</v>
       </c>
       <c r="B75" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" t="s">
         <v>71</v>
-      </c>
-      <c r="C75" t="s">
-        <v>73</v>
       </c>
       <c r="D75" t="n">
         <v>0.0470927917164476</v>
@@ -11866,10 +11866,10 @@
         <v>92</v>
       </c>
       <c r="B76" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" t="s">
         <v>71</v>
-      </c>
-      <c r="C76" t="s">
-        <v>73</v>
       </c>
       <c r="D76" t="n">
         <v>0.0617259288853376</v>
@@ -11892,10 +11892,10 @@
         <v>94</v>
       </c>
       <c r="B77" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" t="s">
         <v>93</v>
-      </c>
-      <c r="C77" t="s">
-        <v>95</v>
       </c>
       <c r="D77" t="n">
         <v>0.125695548489666</v>
@@ -11918,10 +11918,10 @@
         <v>96</v>
       </c>
       <c r="B78" t="s">
+        <v>95</v>
+      </c>
+      <c r="C78" t="s">
         <v>93</v>
-      </c>
-      <c r="C78" t="s">
-        <v>95</v>
       </c>
       <c r="D78" t="n">
         <v>0.171836289763155</v>
@@ -11944,10 +11944,10 @@
         <v>97</v>
       </c>
       <c r="B79" t="s">
+        <v>95</v>
+      </c>
+      <c r="C79" t="s">
         <v>93</v>
-      </c>
-      <c r="C79" t="s">
-        <v>95</v>
       </c>
       <c r="D79" t="n">
         <v>0.203529295132349</v>
@@ -11970,10 +11970,10 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
+        <v>95</v>
+      </c>
+      <c r="C80" t="s">
         <v>93</v>
-      </c>
-      <c r="C80" t="s">
-        <v>95</v>
       </c>
       <c r="D80" t="n">
         <v>0.132300357568534</v>
@@ -11996,10 +11996,10 @@
         <v>99</v>
       </c>
       <c r="B81" t="s">
+        <v>95</v>
+      </c>
+      <c r="C81" t="s">
         <v>93</v>
-      </c>
-      <c r="C81" t="s">
-        <v>95</v>
       </c>
       <c r="D81" t="n">
         <v>0.0837130968892413</v>
@@ -12022,10 +12022,10 @@
         <v>100</v>
       </c>
       <c r="B82" t="s">
+        <v>95</v>
+      </c>
+      <c r="C82" t="s">
         <v>93</v>
-      </c>
-      <c r="C82" t="s">
-        <v>95</v>
       </c>
       <c r="D82" t="n">
         <v>0.0639633356580651</v>
@@ -12048,10 +12048,10 @@
         <v>101</v>
       </c>
       <c r="B83" t="s">
+        <v>95</v>
+      </c>
+      <c r="C83" t="s">
         <v>93</v>
-      </c>
-      <c r="C83" t="s">
-        <v>95</v>
       </c>
       <c r="D83" t="n">
         <v>0.103677932405567</v>
@@ -12074,10 +12074,10 @@
         <v>102</v>
       </c>
       <c r="B84" t="s">
+        <v>95</v>
+      </c>
+      <c r="C84" t="s">
         <v>93</v>
-      </c>
-      <c r="C84" t="s">
-        <v>95</v>
       </c>
       <c r="D84" t="n">
         <v>0.17455268389662</v>
@@ -12100,10 +12100,10 @@
         <v>103</v>
       </c>
       <c r="B85" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" t="s">
         <v>93</v>
-      </c>
-      <c r="C85" t="s">
-        <v>95</v>
       </c>
       <c r="D85" t="n">
         <v>0.130611839491458</v>
@@ -12126,10 +12126,10 @@
         <v>105</v>
       </c>
       <c r="B86" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" t="s">
         <v>104</v>
-      </c>
-      <c r="C86" t="s">
-        <v>106</v>
       </c>
       <c r="D86" t="n">
         <v>0.521730502083746</v>
@@ -12152,10 +12152,10 @@
         <v>107</v>
       </c>
       <c r="B87" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" t="s">
         <v>104</v>
-      </c>
-      <c r="C87" t="s">
-        <v>106</v>
       </c>
       <c r="D87" t="n">
         <v>0.380513430468827</v>
@@ -12178,10 +12178,10 @@
         <v>108</v>
       </c>
       <c r="B88" t="s">
+        <v>106</v>
+      </c>
+      <c r="C88" t="s">
         <v>104</v>
-      </c>
-      <c r="C88" t="s">
-        <v>106</v>
       </c>
       <c r="D88" t="n">
         <v>0.188381330685203</v>
@@ -12204,10 +12204,10 @@
         <v>109</v>
       </c>
       <c r="B89" t="s">
+        <v>106</v>
+      </c>
+      <c r="C89" t="s">
         <v>104</v>
-      </c>
-      <c r="C89" t="s">
-        <v>106</v>
       </c>
       <c r="D89" t="n">
         <v>0.155553343949045</v>
@@ -12230,10 +12230,10 @@
         <v>110</v>
       </c>
       <c r="B90" t="s">
+        <v>106</v>
+      </c>
+      <c r="C90" t="s">
         <v>104</v>
-      </c>
-      <c r="C90" t="s">
-        <v>106</v>
       </c>
       <c r="D90" t="n">
         <v>0.138684681104709</v>
@@ -12256,10 +12256,10 @@
         <v>111</v>
       </c>
       <c r="B91" t="s">
+        <v>106</v>
+      </c>
+      <c r="C91" t="s">
         <v>104</v>
-      </c>
-      <c r="C91" t="s">
-        <v>106</v>
       </c>
       <c r="D91" t="n">
         <v>0.0795658235411272</v>
@@ -12282,10 +12282,10 @@
         <v>112</v>
       </c>
       <c r="B92" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92" t="s">
         <v>104</v>
-      </c>
-      <c r="C92" t="s">
-        <v>106</v>
       </c>
       <c r="D92" t="n">
         <v>0.699406528189911</v>
@@ -12308,10 +12308,10 @@
         <v>113</v>
       </c>
       <c r="B93" t="s">
+        <v>106</v>
+      </c>
+      <c r="C93" t="s">
         <v>104</v>
-      </c>
-      <c r="C93" t="s">
-        <v>106</v>
       </c>
       <c r="D93" t="n">
         <v>0.132182197082465</v>
@@ -12334,10 +12334,10 @@
         <v>114</v>
       </c>
       <c r="B94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C94" t="s">
         <v>104</v>
-      </c>
-      <c r="C94" t="s">
-        <v>106</v>
       </c>
       <c r="D94" t="n">
         <v>0.330232092837135</v>
@@ -12360,10 +12360,10 @@
         <v>116</v>
       </c>
       <c r="B95" t="s">
+        <v>117</v>
+      </c>
+      <c r="C95" t="s">
         <v>115</v>
-      </c>
-      <c r="C95" t="s">
-        <v>117</v>
       </c>
       <c r="D95" t="n">
         <v>0.140417080436941</v>
@@ -12386,10 +12386,10 @@
         <v>118</v>
       </c>
       <c r="B96" t="s">
+        <v>117</v>
+      </c>
+      <c r="C96" t="s">
         <v>115</v>
-      </c>
-      <c r="C96" t="s">
-        <v>117</v>
       </c>
       <c r="D96" t="n">
         <v>0.167328699106256</v>
@@ -12412,10 +12412,10 @@
         <v>119</v>
       </c>
       <c r="B97" t="s">
+        <v>117</v>
+      </c>
+      <c r="C97" t="s">
         <v>115</v>
-      </c>
-      <c r="C97" t="s">
-        <v>117</v>
       </c>
       <c r="D97" t="n">
         <v>0.217214335351931</v>
@@ -12438,10 +12438,10 @@
         <v>120</v>
       </c>
       <c r="B98" t="s">
+        <v>117</v>
+      </c>
+      <c r="C98" t="s">
         <v>115</v>
-      </c>
-      <c r="C98" t="s">
-        <v>117</v>
       </c>
       <c r="D98" t="n">
         <v>0.117897868120972</v>
@@ -12464,10 +12464,10 @@
         <v>121</v>
       </c>
       <c r="B99" t="s">
+        <v>117</v>
+      </c>
+      <c r="C99" t="s">
         <v>115</v>
-      </c>
-      <c r="C99" t="s">
-        <v>117</v>
       </c>
       <c r="D99" t="n">
         <v>0.0693561208267091</v>
@@ -12490,10 +12490,10 @@
         <v>122</v>
       </c>
       <c r="B100" t="s">
+        <v>117</v>
+      </c>
+      <c r="C100" t="s">
         <v>115</v>
-      </c>
-      <c r="C100" t="s">
-        <v>117</v>
       </c>
       <c r="D100" t="n">
         <v>0.0488605831426013</v>
@@ -12516,10 +12516,10 @@
         <v>123</v>
       </c>
       <c r="B101" t="s">
+        <v>117</v>
+      </c>
+      <c r="C101" t="s">
         <v>115</v>
-      </c>
-      <c r="C101" t="s">
-        <v>117</v>
       </c>
       <c r="D101" t="n">
         <v>0.047940446650124</v>
@@ -12542,10 +12542,10 @@
         <v>124</v>
       </c>
       <c r="B102" t="s">
+        <v>117</v>
+      </c>
+      <c r="C102" t="s">
         <v>115</v>
-      </c>
-      <c r="C102" t="s">
-        <v>117</v>
       </c>
       <c r="D102" t="n">
         <v>0.104526503871352</v>
@@ -12568,10 +12568,10 @@
         <v>126</v>
       </c>
       <c r="B103" t="s">
+        <v>127</v>
+      </c>
+      <c r="C103" t="s">
         <v>125</v>
-      </c>
-      <c r="C103" t="s">
-        <v>127</v>
       </c>
       <c r="D103" t="n">
         <v>0.114876279439531</v>
@@ -12594,10 +12594,10 @@
         <v>128</v>
       </c>
       <c r="B104" t="s">
+        <v>127</v>
+      </c>
+      <c r="C104" t="s">
         <v>125</v>
-      </c>
-      <c r="C104" t="s">
-        <v>127</v>
       </c>
       <c r="D104" t="n">
         <v>0.134985133795837</v>
@@ -12620,10 +12620,10 @@
         <v>129</v>
       </c>
       <c r="B105" t="s">
+        <v>127</v>
+      </c>
+      <c r="C105" t="s">
         <v>125</v>
-      </c>
-      <c r="C105" t="s">
-        <v>127</v>
       </c>
       <c r="D105" t="n">
         <v>0.113319489765648</v>
@@ -12646,10 +12646,10 @@
         <v>130</v>
       </c>
       <c r="B106" t="s">
+        <v>127</v>
+      </c>
+      <c r="C106" t="s">
         <v>125</v>
-      </c>
-      <c r="C106" t="s">
-        <v>127</v>
       </c>
       <c r="D106" t="n">
         <v>0.122852318998908</v>
@@ -12672,10 +12672,10 @@
         <v>131</v>
       </c>
       <c r="B107" t="s">
+        <v>127</v>
+      </c>
+      <c r="C107" t="s">
         <v>125</v>
-      </c>
-      <c r="C107" t="s">
-        <v>127</v>
       </c>
       <c r="D107" t="n">
         <v>0.245466386133654</v>
@@ -12698,10 +12698,10 @@
         <v>132</v>
       </c>
       <c r="B108" t="s">
+        <v>127</v>
+      </c>
+      <c r="C108" t="s">
         <v>125</v>
-      </c>
-      <c r="C108" t="s">
-        <v>127</v>
       </c>
       <c r="D108" t="n">
         <v>0.118852459016393</v>
@@ -12724,10 +12724,10 @@
         <v>133</v>
       </c>
       <c r="B109" t="s">
+        <v>127</v>
+      </c>
+      <c r="C109" t="s">
         <v>125</v>
-      </c>
-      <c r="C109" t="s">
-        <v>127</v>
       </c>
       <c r="D109" t="n">
         <v>0.0513794482207117</v>
@@ -12750,10 +12750,10 @@
         <v>134</v>
       </c>
       <c r="B110" t="s">
+        <v>127</v>
+      </c>
+      <c r="C110" t="s">
         <v>125</v>
-      </c>
-      <c r="C110" t="s">
-        <v>127</v>
       </c>
       <c r="D110" t="n">
         <v>0.0567619432380568</v>
@@ -12776,10 +12776,10 @@
         <v>136</v>
       </c>
       <c r="B111" t="s">
+        <v>137</v>
+      </c>
+      <c r="C111" t="s">
         <v>135</v>
-      </c>
-      <c r="C111" t="s">
-        <v>137</v>
       </c>
       <c r="D111" t="n">
         <v>0.098102219098303</v>
@@ -12802,10 +12802,10 @@
         <v>138</v>
       </c>
       <c r="B112" t="s">
+        <v>137</v>
+      </c>
+      <c r="C112" t="s">
         <v>135</v>
-      </c>
-      <c r="C112" t="s">
-        <v>137</v>
       </c>
       <c r="D112" t="n">
         <v>0.105257846402261</v>
@@ -12828,10 +12828,10 @@
         <v>139</v>
       </c>
       <c r="B113" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" t="s">
         <v>135</v>
-      </c>
-      <c r="C113" t="s">
-        <v>137</v>
       </c>
       <c r="D113" t="n">
         <v>0.0539990305380513</v>
@@ -12854,10 +12854,10 @@
         <v>140</v>
       </c>
       <c r="B114" t="s">
+        <v>137</v>
+      </c>
+      <c r="C114" t="s">
         <v>135</v>
-      </c>
-      <c r="C114" t="s">
-        <v>137</v>
       </c>
       <c r="D114" t="n">
         <v>0.111803084223013</v>
@@ -12880,10 +12880,10 @@
         <v>141</v>
       </c>
       <c r="B115" t="s">
+        <v>137</v>
+      </c>
+      <c r="C115" t="s">
         <v>135</v>
-      </c>
-      <c r="C115" t="s">
-        <v>137</v>
       </c>
       <c r="D115" t="n">
         <v>0.0834328952608522</v>
@@ -12906,10 +12906,10 @@
         <v>142</v>
       </c>
       <c r="B116" t="s">
+        <v>137</v>
+      </c>
+      <c r="C116" t="s">
         <v>135</v>
-      </c>
-      <c r="C116" t="s">
-        <v>137</v>
       </c>
       <c r="D116" t="n">
         <v>0.27031408308004</v>
@@ -12932,10 +12932,10 @@
         <v>143</v>
       </c>
       <c r="B117" t="s">
+        <v>137</v>
+      </c>
+      <c r="C117" t="s">
         <v>135</v>
-      </c>
-      <c r="C117" t="s">
-        <v>137</v>
       </c>
       <c r="D117" t="n">
         <v>0.049091456681056</v>
@@ -12958,10 +12958,10 @@
         <v>144</v>
       </c>
       <c r="B118" t="s">
+        <v>137</v>
+      </c>
+      <c r="C118" t="s">
         <v>135</v>
-      </c>
-      <c r="C118" t="s">
-        <v>137</v>
       </c>
       <c r="D118" t="n">
         <v>0.090174694537009</v>
@@ -12984,10 +12984,10 @@
         <v>145</v>
       </c>
       <c r="B119" t="s">
+        <v>137</v>
+      </c>
+      <c r="C119" t="s">
         <v>135</v>
-      </c>
-      <c r="C119" t="s">
-        <v>137</v>
       </c>
       <c r="D119" t="n">
         <v>0.0504432895139101</v>
@@ -13010,10 +13010,10 @@
         <v>146</v>
       </c>
       <c r="B120" t="s">
+        <v>137</v>
+      </c>
+      <c r="C120" t="s">
         <v>135</v>
-      </c>
-      <c r="C120" t="s">
-        <v>137</v>
       </c>
       <c r="D120" t="n">
         <v>0.0524596654459072</v>
@@ -13036,10 +13036,10 @@
         <v>147</v>
       </c>
       <c r="B121" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" t="s">
         <v>135</v>
-      </c>
-      <c r="C121" t="s">
-        <v>137</v>
       </c>
       <c r="D121" t="n">
         <v>0.139904610492845</v>
@@ -13062,10 +13062,10 @@
         <v>148</v>
       </c>
       <c r="B122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" t="s">
         <v>135</v>
-      </c>
-      <c r="C122" t="s">
-        <v>137</v>
       </c>
       <c r="D122" t="n">
         <v>0.130303620085637</v>
@@ -13088,10 +13088,10 @@
         <v>150</v>
       </c>
       <c r="B123" t="s">
+        <v>151</v>
+      </c>
+      <c r="C123" t="s">
         <v>149</v>
-      </c>
-      <c r="C123" t="s">
-        <v>151</v>
       </c>
       <c r="D123" t="n">
         <v>0.0512096774193549</v>
@@ -13114,10 +13114,10 @@
         <v>152</v>
       </c>
       <c r="B124" t="s">
+        <v>151</v>
+      </c>
+      <c r="C124" t="s">
         <v>149</v>
-      </c>
-      <c r="C124" t="s">
-        <v>151</v>
       </c>
       <c r="D124" t="n">
         <v>0.113584868485863</v>
@@ -13140,10 +13140,10 @@
         <v>153</v>
       </c>
       <c r="B125" t="s">
+        <v>151</v>
+      </c>
+      <c r="C125" t="s">
         <v>149</v>
-      </c>
-      <c r="C125" t="s">
-        <v>151</v>
       </c>
       <c r="D125" t="n">
         <v>0.175656847133758</v>
@@ -13166,10 +13166,10 @@
         <v>154</v>
       </c>
       <c r="B126" t="s">
+        <v>151</v>
+      </c>
+      <c r="C126" t="s">
         <v>149</v>
-      </c>
-      <c r="C126" t="s">
-        <v>151</v>
       </c>
       <c r="D126" t="n">
         <v>0.147910285544907</v>
@@ -13192,10 +13192,10 @@
         <v>155</v>
       </c>
       <c r="B127" t="s">
+        <v>151</v>
+      </c>
+      <c r="C127" t="s">
         <v>149</v>
-      </c>
-      <c r="C127" t="s">
-        <v>151</v>
       </c>
       <c r="D127" t="n">
         <v>0.114571967066759</v>
@@ -13218,10 +13218,10 @@
         <v>156</v>
       </c>
       <c r="B128" t="s">
+        <v>151</v>
+      </c>
+      <c r="C128" t="s">
         <v>149</v>
-      </c>
-      <c r="C128" t="s">
-        <v>151</v>
       </c>
       <c r="D128" t="n">
         <v>0.13106315581073</v>
@@ -13244,10 +13244,10 @@
         <v>157</v>
       </c>
       <c r="B129" t="s">
+        <v>151</v>
+      </c>
+      <c r="C129" t="s">
         <v>149</v>
-      </c>
-      <c r="C129" t="s">
-        <v>151</v>
       </c>
       <c r="D129" t="n">
         <v>0.207463129763437</v>
@@ -13270,10 +13270,10 @@
         <v>158</v>
       </c>
       <c r="B130" t="s">
+        <v>151</v>
+      </c>
+      <c r="C130" t="s">
         <v>149</v>
-      </c>
-      <c r="C130" t="s">
-        <v>151</v>
       </c>
       <c r="D130" t="n">
         <v>0.153116260487415</v>
@@ -13296,10 +13296,10 @@
         <v>159</v>
       </c>
       <c r="B131" t="s">
+        <v>151</v>
+      </c>
+      <c r="C131" t="s">
         <v>149</v>
-      </c>
-      <c r="C131" t="s">
-        <v>151</v>
       </c>
       <c r="D131" t="n">
         <v>0.0852436240944726</v>
@@ -13322,10 +13322,10 @@
         <v>160</v>
       </c>
       <c r="B132" t="s">
+        <v>151</v>
+      </c>
+      <c r="C132" t="s">
         <v>149</v>
-      </c>
-      <c r="C132" t="s">
-        <v>151</v>
       </c>
       <c r="D132" t="n">
         <v>0.0645256334708309</v>
@@ -13348,10 +13348,10 @@
         <v>161</v>
       </c>
       <c r="B133" t="s">
+        <v>151</v>
+      </c>
+      <c r="C133" t="s">
         <v>149</v>
-      </c>
-      <c r="C133" t="s">
-        <v>151</v>
       </c>
       <c r="D133" t="n">
         <v>0.375</v>
@@ -13370,10 +13370,10 @@
         <v>162</v>
       </c>
       <c r="B134" t="s">
+        <v>151</v>
+      </c>
+      <c r="C134" t="s">
         <v>149</v>
-      </c>
-      <c r="C134" t="s">
-        <v>151</v>
       </c>
       <c r="D134" t="n">
         <v>0.119142717973697</v>
@@ -13396,10 +13396,10 @@
         <v>163</v>
       </c>
       <c r="B135" t="s">
+        <v>151</v>
+      </c>
+      <c r="C135" t="s">
         <v>149</v>
-      </c>
-      <c r="C135" t="s">
-        <v>151</v>
       </c>
       <c r="D135" t="n">
         <v>0.183573398712841</v>
@@ -13422,10 +13422,10 @@
         <v>164</v>
       </c>
       <c r="B136" t="s">
+        <v>151</v>
+      </c>
+      <c r="C136" t="s">
         <v>149</v>
-      </c>
-      <c r="C136" t="s">
-        <v>151</v>
       </c>
       <c r="D136" t="n">
         <v>0.133573645739461</v>
@@ -13448,10 +13448,10 @@
         <v>165</v>
       </c>
       <c r="B137" t="s">
+        <v>151</v>
+      </c>
+      <c r="C137" t="s">
         <v>149</v>
-      </c>
-      <c r="C137" t="s">
-        <v>151</v>
       </c>
       <c r="D137" t="n">
         <v>0.0599652671365818</v>
@@ -13474,10 +13474,10 @@
         <v>166</v>
       </c>
       <c r="B138" t="s">
+        <v>151</v>
+      </c>
+      <c r="C138" t="s">
         <v>149</v>
-      </c>
-      <c r="C138" t="s">
-        <v>151</v>
       </c>
       <c r="D138" t="n">
         <v>0.0579073482428116</v>
@@ -13500,10 +13500,10 @@
         <v>167</v>
       </c>
       <c r="B139" t="s">
+        <v>151</v>
+      </c>
+      <c r="C139" t="s">
         <v>149</v>
-      </c>
-      <c r="C139" t="s">
-        <v>151</v>
       </c>
       <c r="D139" t="n">
         <v>0.132884202304238</v>
@@ -13537,10 +13537,10 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D1" t="s">
         <v>174</v>
@@ -13563,10 +13563,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -13589,10 +13589,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -13615,10 +13615,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -13641,10 +13641,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -13667,10 +13667,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -13693,10 +13693,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -13719,10 +13719,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -13745,10 +13745,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -13771,10 +13771,10 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -13797,10 +13797,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
         <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -13820,13 +13820,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
         <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -13849,10 +13849,10 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -13875,10 +13875,10 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -13901,10 +13901,10 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -13927,10 +13927,10 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -13950,13 +13950,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
         <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -14005,10 +14005,10 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -14031,10 +14031,10 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -14057,10 +14057,10 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -14083,10 +14083,10 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -14109,10 +14109,10 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -14135,10 +14135,10 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -14161,10 +14161,10 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -14187,10 +14187,10 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -14213,10 +14213,10 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -14239,10 +14239,10 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -14265,10 +14265,10 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
         <v>39</v>
-      </c>
-      <c r="C29" t="s">
-        <v>41</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -14291,10 +14291,10 @@
         <v>42</v>
       </c>
       <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s">
         <v>39</v>
-      </c>
-      <c r="C30" t="s">
-        <v>41</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -14317,10 +14317,10 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s">
         <v>39</v>
-      </c>
-      <c r="C31" t="s">
-        <v>41</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -14343,10 +14343,10 @@
         <v>44</v>
       </c>
       <c r="B32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" t="s">
         <v>39</v>
-      </c>
-      <c r="C32" t="s">
-        <v>41</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -14369,10 +14369,10 @@
         <v>45</v>
       </c>
       <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" t="s">
         <v>39</v>
-      </c>
-      <c r="C33" t="s">
-        <v>41</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -14395,10 +14395,10 @@
         <v>46</v>
       </c>
       <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
         <v>39</v>
-      </c>
-      <c r="C34" t="s">
-        <v>41</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -14421,10 +14421,10 @@
         <v>47</v>
       </c>
       <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s">
         <v>39</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -14447,10 +14447,10 @@
         <v>48</v>
       </c>
       <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
         <v>39</v>
-      </c>
-      <c r="C36" t="s">
-        <v>41</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -14473,10 +14473,10 @@
         <v>49</v>
       </c>
       <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" t="s">
         <v>39</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -14499,10 +14499,10 @@
         <v>50</v>
       </c>
       <c r="B38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s">
         <v>39</v>
-      </c>
-      <c r="C38" t="s">
-        <v>41</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -14525,10 +14525,10 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" t="s">
         <v>39</v>
-      </c>
-      <c r="C39" t="s">
-        <v>41</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -14551,10 +14551,10 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" t="s">
         <v>39</v>
-      </c>
-      <c r="C40" t="s">
-        <v>41</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -14577,10 +14577,10 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s">
         <v>39</v>
-      </c>
-      <c r="C41" t="s">
-        <v>41</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -14603,10 +14603,10 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s">
         <v>39</v>
-      </c>
-      <c r="C42" t="s">
-        <v>41</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -14629,10 +14629,10 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s">
         <v>39</v>
-      </c>
-      <c r="C43" t="s">
-        <v>41</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -14655,10 +14655,10 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s">
         <v>39</v>
-      </c>
-      <c r="C44" t="s">
-        <v>41</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -14681,10 +14681,10 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" t="s">
         <v>39</v>
-      </c>
-      <c r="C45" t="s">
-        <v>41</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -14707,10 +14707,10 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" t="s">
         <v>58</v>
-      </c>
-      <c r="C46" t="s">
-        <v>60</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -14733,10 +14733,10 @@
         <v>61</v>
       </c>
       <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="s">
         <v>58</v>
-      </c>
-      <c r="C47" t="s">
-        <v>60</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -14759,10 +14759,10 @@
         <v>62</v>
       </c>
       <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" t="s">
         <v>58</v>
-      </c>
-      <c r="C48" t="s">
-        <v>60</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -14785,10 +14785,10 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" t="s">
         <v>58</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -14811,10 +14811,10 @@
         <v>64</v>
       </c>
       <c r="B50" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" t="s">
         <v>58</v>
-      </c>
-      <c r="C50" t="s">
-        <v>60</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -14837,10 +14837,10 @@
         <v>65</v>
       </c>
       <c r="B51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" t="s">
         <v>58</v>
-      </c>
-      <c r="C51" t="s">
-        <v>60</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -14863,10 +14863,10 @@
         <v>66</v>
       </c>
       <c r="B52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" t="s">
         <v>58</v>
-      </c>
-      <c r="C52" t="s">
-        <v>60</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -14889,10 +14889,10 @@
         <v>67</v>
       </c>
       <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" t="s">
         <v>58</v>
-      </c>
-      <c r="C53" t="s">
-        <v>60</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>68</v>
       </c>
       <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" t="s">
         <v>58</v>
-      </c>
-      <c r="C54" t="s">
-        <v>60</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -14941,10 +14941,10 @@
         <v>69</v>
       </c>
       <c r="B55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" t="s">
         <v>58</v>
-      </c>
-      <c r="C55" t="s">
-        <v>60</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -14967,10 +14967,10 @@
         <v>70</v>
       </c>
       <c r="B56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" t="s">
         <v>58</v>
-      </c>
-      <c r="C56" t="s">
-        <v>60</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -14993,10 +14993,10 @@
         <v>72</v>
       </c>
       <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
         <v>71</v>
-      </c>
-      <c r="C57" t="s">
-        <v>73</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -15019,10 +15019,10 @@
         <v>74</v>
       </c>
       <c r="B58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" t="s">
         <v>71</v>
-      </c>
-      <c r="C58" t="s">
-        <v>73</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -15045,10 +15045,10 @@
         <v>75</v>
       </c>
       <c r="B59" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" t="s">
         <v>71</v>
-      </c>
-      <c r="C59" t="s">
-        <v>73</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -15071,10 +15071,10 @@
         <v>76</v>
       </c>
       <c r="B60" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" t="s">
         <v>71</v>
-      </c>
-      <c r="C60" t="s">
-        <v>73</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -15097,10 +15097,10 @@
         <v>77</v>
       </c>
       <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
         <v>71</v>
-      </c>
-      <c r="C61" t="s">
-        <v>73</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -15123,10 +15123,10 @@
         <v>78</v>
       </c>
       <c r="B62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" t="s">
         <v>71</v>
-      </c>
-      <c r="C62" t="s">
-        <v>73</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -15149,10 +15149,10 @@
         <v>79</v>
       </c>
       <c r="B63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" t="s">
         <v>71</v>
-      </c>
-      <c r="C63" t="s">
-        <v>73</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -15175,10 +15175,10 @@
         <v>80</v>
       </c>
       <c r="B64" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" t="s">
         <v>71</v>
-      </c>
-      <c r="C64" t="s">
-        <v>73</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -15201,10 +15201,10 @@
         <v>81</v>
       </c>
       <c r="B65" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" t="s">
         <v>71</v>
-      </c>
-      <c r="C65" t="s">
-        <v>73</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>82</v>
       </c>
       <c r="B66" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" t="s">
         <v>71</v>
-      </c>
-      <c r="C66" t="s">
-        <v>73</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -15253,10 +15253,10 @@
         <v>83</v>
       </c>
       <c r="B67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" t="s">
         <v>71</v>
-      </c>
-      <c r="C67" t="s">
-        <v>73</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -15279,10 +15279,10 @@
         <v>84</v>
       </c>
       <c r="B68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" t="s">
         <v>71</v>
-      </c>
-      <c r="C68" t="s">
-        <v>73</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -15305,10 +15305,10 @@
         <v>85</v>
       </c>
       <c r="B69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" t="s">
         <v>71</v>
-      </c>
-      <c r="C69" t="s">
-        <v>73</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -15331,10 +15331,10 @@
         <v>86</v>
       </c>
       <c r="B70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" t="s">
         <v>71</v>
-      </c>
-      <c r="C70" t="s">
-        <v>73</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -15357,10 +15357,10 @@
         <v>87</v>
       </c>
       <c r="B71" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" t="s">
         <v>71</v>
-      </c>
-      <c r="C71" t="s">
-        <v>73</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -15383,10 +15383,10 @@
         <v>88</v>
       </c>
       <c r="B72" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" t="s">
         <v>71</v>
-      </c>
-      <c r="C72" t="s">
-        <v>73</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -15409,10 +15409,10 @@
         <v>89</v>
       </c>
       <c r="B73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" t="s">
         <v>71</v>
-      </c>
-      <c r="C73" t="s">
-        <v>73</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -15435,10 +15435,10 @@
         <v>90</v>
       </c>
       <c r="B74" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" t="s">
         <v>71</v>
-      </c>
-      <c r="C74" t="s">
-        <v>73</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -15461,10 +15461,10 @@
         <v>91</v>
       </c>
       <c r="B75" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" t="s">
         <v>71</v>
-      </c>
-      <c r="C75" t="s">
-        <v>73</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -15487,10 +15487,10 @@
         <v>92</v>
       </c>
       <c r="B76" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" t="s">
         <v>71</v>
-      </c>
-      <c r="C76" t="s">
-        <v>73</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -15513,10 +15513,10 @@
         <v>94</v>
       </c>
       <c r="B77" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" t="s">
         <v>93</v>
-      </c>
-      <c r="C77" t="s">
-        <v>95</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -15539,10 +15539,10 @@
         <v>96</v>
       </c>
       <c r="B78" t="s">
+        <v>95</v>
+      </c>
+      <c r="C78" t="s">
         <v>93</v>
-      </c>
-      <c r="C78" t="s">
-        <v>95</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -15565,10 +15565,10 @@
         <v>97</v>
       </c>
       <c r="B79" t="s">
+        <v>95</v>
+      </c>
+      <c r="C79" t="s">
         <v>93</v>
-      </c>
-      <c r="C79" t="s">
-        <v>95</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -15591,10 +15591,10 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
+        <v>95</v>
+      </c>
+      <c r="C80" t="s">
         <v>93</v>
-      </c>
-      <c r="C80" t="s">
-        <v>95</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -15617,10 +15617,10 @@
         <v>99</v>
       </c>
       <c r="B81" t="s">
+        <v>95</v>
+      </c>
+      <c r="C81" t="s">
         <v>93</v>
-      </c>
-      <c r="C81" t="s">
-        <v>95</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -15643,10 +15643,10 @@
         <v>100</v>
       </c>
       <c r="B82" t="s">
+        <v>95</v>
+      </c>
+      <c r="C82" t="s">
         <v>93</v>
-      </c>
-      <c r="C82" t="s">
-        <v>95</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -15669,10 +15669,10 @@
         <v>101</v>
       </c>
       <c r="B83" t="s">
+        <v>95</v>
+      </c>
+      <c r="C83" t="s">
         <v>93</v>
-      </c>
-      <c r="C83" t="s">
-        <v>95</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -15695,10 +15695,10 @@
         <v>102</v>
       </c>
       <c r="B84" t="s">
+        <v>95</v>
+      </c>
+      <c r="C84" t="s">
         <v>93</v>
-      </c>
-      <c r="C84" t="s">
-        <v>95</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -15721,10 +15721,10 @@
         <v>103</v>
       </c>
       <c r="B85" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" t="s">
         <v>93</v>
-      </c>
-      <c r="C85" t="s">
-        <v>95</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -15747,10 +15747,10 @@
         <v>105</v>
       </c>
       <c r="B86" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" t="s">
         <v>104</v>
-      </c>
-      <c r="C86" t="s">
-        <v>106</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -15773,10 +15773,10 @@
         <v>107</v>
       </c>
       <c r="B87" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" t="s">
         <v>104</v>
-      </c>
-      <c r="C87" t="s">
-        <v>106</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -15799,10 +15799,10 @@
         <v>108</v>
       </c>
       <c r="B88" t="s">
+        <v>106</v>
+      </c>
+      <c r="C88" t="s">
         <v>104</v>
-      </c>
-      <c r="C88" t="s">
-        <v>106</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -15825,10 +15825,10 @@
         <v>109</v>
       </c>
       <c r="B89" t="s">
+        <v>106</v>
+      </c>
+      <c r="C89" t="s">
         <v>104</v>
-      </c>
-      <c r="C89" t="s">
-        <v>106</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -15851,10 +15851,10 @@
         <v>110</v>
       </c>
       <c r="B90" t="s">
+        <v>106</v>
+      </c>
+      <c r="C90" t="s">
         <v>104</v>
-      </c>
-      <c r="C90" t="s">
-        <v>106</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -15877,10 +15877,10 @@
         <v>111</v>
       </c>
       <c r="B91" t="s">
+        <v>106</v>
+      </c>
+      <c r="C91" t="s">
         <v>104</v>
-      </c>
-      <c r="C91" t="s">
-        <v>106</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -15903,10 +15903,10 @@
         <v>112</v>
       </c>
       <c r="B92" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92" t="s">
         <v>104</v>
-      </c>
-      <c r="C92" t="s">
-        <v>106</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -15929,10 +15929,10 @@
         <v>113</v>
       </c>
       <c r="B93" t="s">
+        <v>106</v>
+      </c>
+      <c r="C93" t="s">
         <v>104</v>
-      </c>
-      <c r="C93" t="s">
-        <v>106</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -15955,10 +15955,10 @@
         <v>114</v>
       </c>
       <c r="B94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C94" t="s">
         <v>104</v>
-      </c>
-      <c r="C94" t="s">
-        <v>106</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -15981,10 +15981,10 @@
         <v>116</v>
       </c>
       <c r="B95" t="s">
+        <v>117</v>
+      </c>
+      <c r="C95" t="s">
         <v>115</v>
-      </c>
-      <c r="C95" t="s">
-        <v>117</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -16007,10 +16007,10 @@
         <v>118</v>
       </c>
       <c r="B96" t="s">
+        <v>117</v>
+      </c>
+      <c r="C96" t="s">
         <v>115</v>
-      </c>
-      <c r="C96" t="s">
-        <v>117</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -16033,10 +16033,10 @@
         <v>119</v>
       </c>
       <c r="B97" t="s">
+        <v>117</v>
+      </c>
+      <c r="C97" t="s">
         <v>115</v>
-      </c>
-      <c r="C97" t="s">
-        <v>117</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>120</v>
       </c>
       <c r="B98" t="s">
+        <v>117</v>
+      </c>
+      <c r="C98" t="s">
         <v>115</v>
-      </c>
-      <c r="C98" t="s">
-        <v>117</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -16085,10 +16085,10 @@
         <v>121</v>
       </c>
       <c r="B99" t="s">
+        <v>117</v>
+      </c>
+      <c r="C99" t="s">
         <v>115</v>
-      </c>
-      <c r="C99" t="s">
-        <v>117</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -16111,10 +16111,10 @@
         <v>122</v>
       </c>
       <c r="B100" t="s">
+        <v>117</v>
+      </c>
+      <c r="C100" t="s">
         <v>115</v>
-      </c>
-      <c r="C100" t="s">
-        <v>117</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -16137,10 +16137,10 @@
         <v>123</v>
       </c>
       <c r="B101" t="s">
+        <v>117</v>
+      </c>
+      <c r="C101" t="s">
         <v>115</v>
-      </c>
-      <c r="C101" t="s">
-        <v>117</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -16163,10 +16163,10 @@
         <v>124</v>
       </c>
       <c r="B102" t="s">
+        <v>117</v>
+      </c>
+      <c r="C102" t="s">
         <v>115</v>
-      </c>
-      <c r="C102" t="s">
-        <v>117</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -16189,10 +16189,10 @@
         <v>126</v>
       </c>
       <c r="B103" t="s">
+        <v>127</v>
+      </c>
+      <c r="C103" t="s">
         <v>125</v>
-      </c>
-      <c r="C103" t="s">
-        <v>127</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -16215,10 +16215,10 @@
         <v>128</v>
       </c>
       <c r="B104" t="s">
+        <v>127</v>
+      </c>
+      <c r="C104" t="s">
         <v>125</v>
-      </c>
-      <c r="C104" t="s">
-        <v>127</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -16241,10 +16241,10 @@
         <v>129</v>
       </c>
       <c r="B105" t="s">
+        <v>127</v>
+      </c>
+      <c r="C105" t="s">
         <v>125</v>
-      </c>
-      <c r="C105" t="s">
-        <v>127</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -16267,10 +16267,10 @@
         <v>130</v>
       </c>
       <c r="B106" t="s">
+        <v>127</v>
+      </c>
+      <c r="C106" t="s">
         <v>125</v>
-      </c>
-      <c r="C106" t="s">
-        <v>127</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>131</v>
       </c>
       <c r="B107" t="s">
+        <v>127</v>
+      </c>
+      <c r="C107" t="s">
         <v>125</v>
-      </c>
-      <c r="C107" t="s">
-        <v>127</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -16319,10 +16319,10 @@
         <v>132</v>
       </c>
       <c r="B108" t="s">
+        <v>127</v>
+      </c>
+      <c r="C108" t="s">
         <v>125</v>
-      </c>
-      <c r="C108" t="s">
-        <v>127</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -16345,10 +16345,10 @@
         <v>133</v>
       </c>
       <c r="B109" t="s">
+        <v>127</v>
+      </c>
+      <c r="C109" t="s">
         <v>125</v>
-      </c>
-      <c r="C109" t="s">
-        <v>127</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -16371,10 +16371,10 @@
         <v>134</v>
       </c>
       <c r="B110" t="s">
+        <v>127</v>
+      </c>
+      <c r="C110" t="s">
         <v>125</v>
-      </c>
-      <c r="C110" t="s">
-        <v>127</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -16397,10 +16397,10 @@
         <v>136</v>
       </c>
       <c r="B111" t="s">
+        <v>137</v>
+      </c>
+      <c r="C111" t="s">
         <v>135</v>
-      </c>
-      <c r="C111" t="s">
-        <v>137</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -16423,10 +16423,10 @@
         <v>138</v>
       </c>
       <c r="B112" t="s">
+        <v>137</v>
+      </c>
+      <c r="C112" t="s">
         <v>135</v>
-      </c>
-      <c r="C112" t="s">
-        <v>137</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -16449,10 +16449,10 @@
         <v>139</v>
       </c>
       <c r="B113" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" t="s">
         <v>135</v>
-      </c>
-      <c r="C113" t="s">
-        <v>137</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -16475,10 +16475,10 @@
         <v>140</v>
       </c>
       <c r="B114" t="s">
+        <v>137</v>
+      </c>
+      <c r="C114" t="s">
         <v>135</v>
-      </c>
-      <c r="C114" t="s">
-        <v>137</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -16501,10 +16501,10 @@
         <v>141</v>
       </c>
       <c r="B115" t="s">
+        <v>137</v>
+      </c>
+      <c r="C115" t="s">
         <v>135</v>
-      </c>
-      <c r="C115" t="s">
-        <v>137</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -16527,10 +16527,10 @@
         <v>142</v>
       </c>
       <c r="B116" t="s">
+        <v>137</v>
+      </c>
+      <c r="C116" t="s">
         <v>135</v>
-      </c>
-      <c r="C116" t="s">
-        <v>137</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -16553,10 +16553,10 @@
         <v>143</v>
       </c>
       <c r="B117" t="s">
+        <v>137</v>
+      </c>
+      <c r="C117" t="s">
         <v>135</v>
-      </c>
-      <c r="C117" t="s">
-        <v>137</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -16579,10 +16579,10 @@
         <v>144</v>
       </c>
       <c r="B118" t="s">
+        <v>137</v>
+      </c>
+      <c r="C118" t="s">
         <v>135</v>
-      </c>
-      <c r="C118" t="s">
-        <v>137</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -16605,10 +16605,10 @@
         <v>145</v>
       </c>
       <c r="B119" t="s">
+        <v>137</v>
+      </c>
+      <c r="C119" t="s">
         <v>135</v>
-      </c>
-      <c r="C119" t="s">
-        <v>137</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -16631,10 +16631,10 @@
         <v>146</v>
       </c>
       <c r="B120" t="s">
+        <v>137</v>
+      </c>
+      <c r="C120" t="s">
         <v>135</v>
-      </c>
-      <c r="C120" t="s">
-        <v>137</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -16657,10 +16657,10 @@
         <v>147</v>
       </c>
       <c r="B121" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" t="s">
         <v>135</v>
-      </c>
-      <c r="C121" t="s">
-        <v>137</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -16683,10 +16683,10 @@
         <v>148</v>
       </c>
       <c r="B122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" t="s">
         <v>135</v>
-      </c>
-      <c r="C122" t="s">
-        <v>137</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -16709,10 +16709,10 @@
         <v>150</v>
       </c>
       <c r="B123" t="s">
+        <v>151</v>
+      </c>
+      <c r="C123" t="s">
         <v>149</v>
-      </c>
-      <c r="C123" t="s">
-        <v>151</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -16735,10 +16735,10 @@
         <v>152</v>
       </c>
       <c r="B124" t="s">
+        <v>151</v>
+      </c>
+      <c r="C124" t="s">
         <v>149</v>
-      </c>
-      <c r="C124" t="s">
-        <v>151</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -16761,10 +16761,10 @@
         <v>153</v>
       </c>
       <c r="B125" t="s">
+        <v>151</v>
+      </c>
+      <c r="C125" t="s">
         <v>149</v>
-      </c>
-      <c r="C125" t="s">
-        <v>151</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -16787,10 +16787,10 @@
         <v>154</v>
       </c>
       <c r="B126" t="s">
+        <v>151</v>
+      </c>
+      <c r="C126" t="s">
         <v>149</v>
-      </c>
-      <c r="C126" t="s">
-        <v>151</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -16813,10 +16813,10 @@
         <v>155</v>
       </c>
       <c r="B127" t="s">
+        <v>151</v>
+      </c>
+      <c r="C127" t="s">
         <v>149</v>
-      </c>
-      <c r="C127" t="s">
-        <v>151</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -16839,10 +16839,10 @@
         <v>156</v>
       </c>
       <c r="B128" t="s">
+        <v>151</v>
+      </c>
+      <c r="C128" t="s">
         <v>149</v>
-      </c>
-      <c r="C128" t="s">
-        <v>151</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -16865,10 +16865,10 @@
         <v>157</v>
       </c>
       <c r="B129" t="s">
+        <v>151</v>
+      </c>
+      <c r="C129" t="s">
         <v>149</v>
-      </c>
-      <c r="C129" t="s">
-        <v>151</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -16891,10 +16891,10 @@
         <v>158</v>
       </c>
       <c r="B130" t="s">
+        <v>151</v>
+      </c>
+      <c r="C130" t="s">
         <v>149</v>
-      </c>
-      <c r="C130" t="s">
-        <v>151</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -16917,10 +16917,10 @@
         <v>159</v>
       </c>
       <c r="B131" t="s">
+        <v>151</v>
+      </c>
+      <c r="C131" t="s">
         <v>149</v>
-      </c>
-      <c r="C131" t="s">
-        <v>151</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -16943,10 +16943,10 @@
         <v>160</v>
       </c>
       <c r="B132" t="s">
+        <v>151</v>
+      </c>
+      <c r="C132" t="s">
         <v>149</v>
-      </c>
-      <c r="C132" t="s">
-        <v>151</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -16969,10 +16969,10 @@
         <v>161</v>
       </c>
       <c r="B133" t="s">
+        <v>151</v>
+      </c>
+      <c r="C133" t="s">
         <v>149</v>
-      </c>
-      <c r="C133" t="s">
-        <v>151</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -16995,10 +16995,10 @@
         <v>162</v>
       </c>
       <c r="B134" t="s">
+        <v>151</v>
+      </c>
+      <c r="C134" t="s">
         <v>149</v>
-      </c>
-      <c r="C134" t="s">
-        <v>151</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -17021,10 +17021,10 @@
         <v>163</v>
       </c>
       <c r="B135" t="s">
+        <v>151</v>
+      </c>
+      <c r="C135" t="s">
         <v>149</v>
-      </c>
-      <c r="C135" t="s">
-        <v>151</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -17047,10 +17047,10 @@
         <v>164</v>
       </c>
       <c r="B136" t="s">
+        <v>151</v>
+      </c>
+      <c r="C136" t="s">
         <v>149</v>
-      </c>
-      <c r="C136" t="s">
-        <v>151</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -17073,10 +17073,10 @@
         <v>165</v>
       </c>
       <c r="B137" t="s">
+        <v>151</v>
+      </c>
+      <c r="C137" t="s">
         <v>149</v>
-      </c>
-      <c r="C137" t="s">
-        <v>151</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -17099,10 +17099,10 @@
         <v>166</v>
       </c>
       <c r="B138" t="s">
+        <v>151</v>
+      </c>
+      <c r="C138" t="s">
         <v>149</v>
-      </c>
-      <c r="C138" t="s">
-        <v>151</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -17125,10 +17125,10 @@
         <v>167</v>
       </c>
       <c r="B139" t="s">
+        <v>151</v>
+      </c>
+      <c r="C139" t="s">
         <v>149</v>
-      </c>
-      <c r="C139" t="s">
-        <v>151</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -17194,10 +17194,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G2" t="n">
         <v>72</v>
@@ -17217,10 +17217,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G3" t="n">
         <v>72</v>
@@ -17240,10 +17240,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G4" t="n">
         <v>72</v>
@@ -17263,10 +17263,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G5" t="n">
         <v>72</v>
@@ -17286,10 +17286,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G6" t="n">
         <v>72</v>
@@ -17309,10 +17309,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G7" t="n">
         <v>72</v>
@@ -17332,10 +17332,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
@@ -17355,10 +17355,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G9" t="n">
         <v>72</v>
@@ -17378,10 +17378,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G10" t="n">
         <v>72</v>
@@ -17401,10 +17401,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G11" t="n">
         <v>72</v>
@@ -17424,10 +17424,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G12" t="n">
         <v>72</v>
@@ -17447,10 +17447,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G13" t="n">
         <v>72</v>
@@ -17470,10 +17470,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G14" t="n">
         <v>72</v>
@@ -17493,10 +17493,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G15" t="n">
         <v>72</v>
@@ -17516,10 +17516,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G16" t="n">
         <v>72</v>
@@ -17539,10 +17539,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G17" t="n">
         <v>72</v>
@@ -17562,10 +17562,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G18" t="n">
         <v>72</v>
@@ -17585,10 +17585,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G19" t="n">
         <v>72</v>
@@ -17608,10 +17608,10 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G20" t="n">
         <v>72</v>
@@ -17631,10 +17631,10 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G21" t="n">
         <v>72</v>
@@ -17654,10 +17654,10 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G22" t="n">
         <v>72</v>
@@ -17677,10 +17677,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G23" t="n">
         <v>72</v>
@@ -17700,10 +17700,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G24" t="n">
         <v>72</v>
@@ -17723,10 +17723,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G25" t="n">
         <v>72</v>
@@ -17746,10 +17746,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F26" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G26" t="n">
         <v>72</v>
@@ -17769,10 +17769,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G27" t="n">
         <v>72</v>
@@ -17792,10 +17792,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G28" t="n">
         <v>72</v>
@@ -17815,10 +17815,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E29" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G29" t="n">
         <v>72</v>
@@ -17838,10 +17838,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G30" t="n">
         <v>72</v>
@@ -17861,10 +17861,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G31" t="n">
         <v>72</v>
@@ -17884,10 +17884,10 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G32" t="n">
         <v>72</v>
@@ -17907,10 +17907,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G33" t="n">
         <v>72</v>
@@ -17930,10 +17930,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F34" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G34" t="n">
         <v>72</v>
@@ -17953,10 +17953,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G35" t="n">
         <v>72</v>
@@ -17976,10 +17976,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F36" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G36" t="n">
         <v>72</v>
@@ -17999,10 +17999,10 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F37" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G37" t="n">
         <v>72</v>
@@ -18022,10 +18022,10 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F38" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G38" t="n">
         <v>72</v>
@@ -18045,10 +18045,10 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F39" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G39" t="n">
         <v>72</v>
@@ -18068,10 +18068,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E40" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F40" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G40" t="n">
         <v>72</v>
@@ -18091,10 +18091,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E41" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F41" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G41" t="n">
         <v>72</v>
@@ -18114,10 +18114,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E42" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F42" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G42" t="n">
         <v>72</v>
@@ -18137,10 +18137,10 @@
         <v>0.0204081632653061</v>
       </c>
       <c r="E43" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F43" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G43" t="n">
         <v>72</v>
@@ -18160,10 +18160,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E44" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F44" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G44" t="n">
         <v>72</v>
@@ -18183,10 +18183,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E45" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F45" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G45" t="n">
         <v>72</v>
@@ -18206,10 +18206,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E46" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F46" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G46" t="n">
         <v>72</v>
@@ -18229,10 +18229,10 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G47" t="n">
         <v>72</v>
@@ -18252,10 +18252,10 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F48" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G48" t="n">
         <v>72</v>
@@ -18275,10 +18275,10 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G49" t="n">
         <v>72</v>
@@ -18298,10 +18298,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E50" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G50" t="n">
         <v>72</v>
@@ -18321,10 +18321,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E51" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F51" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G51" t="n">
         <v>72</v>
@@ -18344,10 +18344,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E52" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F52" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G52" t="n">
         <v>72</v>
@@ -18367,10 +18367,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E53" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F53" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G53" t="n">
         <v>72</v>
@@ -18390,10 +18390,10 @@
         <v>0.0204081632653061</v>
       </c>
       <c r="E54" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F54" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G54" t="n">
         <v>72</v>
@@ -18413,10 +18413,10 @@
         <v>0.0204081632653061</v>
       </c>
       <c r="E55" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G55" t="n">
         <v>72</v>
@@ -18436,10 +18436,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E56" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G56" t="n">
         <v>72</v>
@@ -18459,10 +18459,10 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G57" t="n">
         <v>72</v>
@@ -18482,10 +18482,10 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G58" t="n">
         <v>72</v>
@@ -18505,10 +18505,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E59" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G59" t="n">
         <v>72</v>
@@ -18528,10 +18528,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E60" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G60" t="n">
         <v>72</v>
@@ -18551,10 +18551,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E61" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G61" t="n">
         <v>72</v>
@@ -18574,10 +18574,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E62" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G62" t="n">
         <v>72</v>
@@ -18597,10 +18597,10 @@
         <v>0.0204081632653061</v>
       </c>
       <c r="E63" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G63" t="n">
         <v>72</v>
@@ -18620,10 +18620,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E64" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G64" t="n">
         <v>72</v>
@@ -18643,10 +18643,10 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G65" t="n">
         <v>72</v>
@@ -18666,10 +18666,10 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G66" t="n">
         <v>72</v>
@@ -18689,10 +18689,10 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G67" t="n">
         <v>72</v>
@@ -18712,10 +18712,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E68" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G68" t="n">
         <v>72</v>
@@ -18735,10 +18735,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E69" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G69" t="n">
         <v>72</v>
@@ -18758,10 +18758,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E70" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G70" t="n">
         <v>72</v>
@@ -18781,10 +18781,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E71" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G71" t="n">
         <v>72</v>
@@ -18804,10 +18804,10 @@
         <v>0.0204081632653061</v>
       </c>
       <c r="E72" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F72" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G72" t="n">
         <v>72</v>
@@ -18827,10 +18827,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E73" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
@@ -18850,10 +18850,10 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F74" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G74" t="n">
         <v>153</v>
@@ -18873,10 +18873,10 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F75" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G75" t="n">
         <v>153</v>
@@ -18896,10 +18896,10 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F76" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G76" t="n">
         <v>153</v>
@@ -18919,10 +18919,10 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F77" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G77" t="n">
         <v>153</v>
@@ -18942,10 +18942,10 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F78" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G78" t="n">
         <v>153</v>
@@ -18965,10 +18965,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E79" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F79" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G79" t="n">
         <v>153</v>
@@ -18988,10 +18988,10 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F80" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G80" t="n">
         <v>153</v>
@@ -19011,10 +19011,10 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F81" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G81" t="n">
         <v>153</v>
@@ -19034,10 +19034,10 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F82" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G82" t="n">
         <v>153</v>
@@ -19057,10 +19057,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E83" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F83" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G83" t="n">
         <v>153</v>
@@ -19080,10 +19080,10 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F84" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G84" t="n">
         <v>153</v>
@@ -19103,10 +19103,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E85" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F85" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G85" t="n">
         <v>153</v>
@@ -19126,10 +19126,10 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F86" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G86" t="n">
         <v>153</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F87" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G87" t="n">
         <v>153</v>
@@ -19172,10 +19172,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E88" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F88" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G88" t="n">
         <v>153</v>
@@ -19195,10 +19195,10 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F89" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G89" t="n">
         <v>153</v>
@@ -19218,10 +19218,10 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F90" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G90" t="n">
         <v>153</v>
@@ -19241,10 +19241,10 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F91" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G91" t="n">
         <v>153</v>
@@ -19264,10 +19264,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E92" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F92" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G92" t="n">
         <v>153</v>
@@ -19287,10 +19287,10 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F93" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G93" t="n">
         <v>153</v>
@@ -19310,10 +19310,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E94" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F94" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G94" t="n">
         <v>153</v>
@@ -19333,10 +19333,10 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F95" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G95" t="n">
         <v>153</v>
@@ -19356,10 +19356,10 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F96" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G96" t="n">
         <v>153</v>
@@ -19379,10 +19379,10 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F97" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G97" t="n">
         <v>153</v>
@@ -19402,10 +19402,10 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F98" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G98" t="n">
         <v>153</v>
@@ -19425,10 +19425,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E99" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F99" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G99" t="n">
         <v>153</v>
@@ -19448,10 +19448,10 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F100" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G100" t="n">
         <v>153</v>
@@ -19471,10 +19471,10 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F101" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G101" t="n">
         <v>153</v>
@@ -19494,10 +19494,10 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F102" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G102" t="n">
         <v>153</v>
@@ -19517,10 +19517,10 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F103" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G103" t="n">
         <v>153</v>
@@ -19540,10 +19540,10 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F104" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G104" t="n">
         <v>153</v>
@@ -19563,10 +19563,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E105" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F105" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G105" t="n">
         <v>153</v>
@@ -19586,10 +19586,10 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F106" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G106" t="n">
         <v>153</v>
@@ -19609,10 +19609,10 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F107" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G107" t="n">
         <v>153</v>
@@ -19632,10 +19632,10 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F108" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G108" t="n">
         <v>153</v>
@@ -19655,10 +19655,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E109" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F109" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G109" t="n">
         <v>153</v>
@@ -19678,10 +19678,10 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F110" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G110" t="n">
         <v>153</v>
@@ -19701,10 +19701,10 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F111" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G111" t="n">
         <v>153</v>
@@ -19724,10 +19724,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E112" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F112" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G112" t="n">
         <v>153</v>
@@ -19747,10 +19747,10 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F113" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G113" t="n">
         <v>153</v>
@@ -19770,10 +19770,10 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F114" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G114" t="n">
         <v>153</v>
@@ -19793,10 +19793,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E115" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F115" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G115" t="n">
         <v>153</v>
@@ -19816,10 +19816,10 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F116" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G116" t="n">
         <v>153</v>
@@ -19839,10 +19839,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E117" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F117" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G117" t="n">
         <v>153</v>
@@ -19862,10 +19862,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E118" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F118" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G118" t="n">
         <v>153</v>
@@ -19885,10 +19885,10 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F119" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G119" t="n">
         <v>153</v>
@@ -19908,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F120" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G120" t="n">
         <v>153</v>
@@ -19931,10 +19931,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E121" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F121" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G121" t="n">
         <v>153</v>
@@ -19954,10 +19954,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E122" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F122" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G122" t="n">
         <v>153</v>
@@ -19977,10 +19977,10 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F123" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G123" t="n">
         <v>153</v>
@@ -20000,10 +20000,10 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F124" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G124" t="n">
         <v>153</v>
@@ -20023,10 +20023,10 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F125" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G125" t="n">
         <v>153</v>
@@ -20046,10 +20046,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E126" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F126" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G126" t="n">
         <v>153</v>
@@ -20069,10 +20069,10 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F127" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G127" t="n">
         <v>153</v>
@@ -20092,10 +20092,10 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F128" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G128" t="n">
         <v>153</v>
@@ -20115,10 +20115,10 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F129" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G129" t="n">
         <v>153</v>
@@ -20138,10 +20138,10 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F130" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G130" t="n">
         <v>153</v>
@@ -20161,10 +20161,10 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F131" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G131" t="n">
         <v>153</v>
@@ -20184,10 +20184,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E132" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F132" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G132" t="n">
         <v>153</v>
@@ -20207,10 +20207,10 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F133" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G133" t="n">
         <v>153</v>
@@ -20230,10 +20230,10 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F134" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G134" t="n">
         <v>153</v>
@@ -20253,10 +20253,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E135" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F135" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G135" t="n">
         <v>153</v>
@@ -20276,10 +20276,10 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F136" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G136" t="n">
         <v>153</v>
@@ -20299,10 +20299,10 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F137" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G137" t="n">
         <v>153</v>
@@ -20322,10 +20322,10 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F138" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G138" t="n">
         <v>153</v>
@@ -20345,10 +20345,10 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F139" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G139" t="n">
         <v>153</v>
@@ -20368,10 +20368,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E140" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F140" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G140" t="n">
         <v>153</v>
@@ -20391,10 +20391,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E141" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F141" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G141" t="n">
         <v>153</v>
@@ -20414,10 +20414,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E142" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F142" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G142" t="n">
         <v>153</v>
@@ -20437,10 +20437,10 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F143" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G143" t="n">
         <v>153</v>
@@ -20460,10 +20460,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E144" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F144" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G144" t="n">
         <v>153</v>
@@ -20483,10 +20483,10 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F145" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G145" t="n">
         <v>153</v>
@@ -20506,10 +20506,10 @@
         <v>0</v>
       </c>
       <c r="E146" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F146" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G146" t="n">
         <v>153</v>
@@ -20529,10 +20529,10 @@
         <v>0</v>
       </c>
       <c r="E147" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F147" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G147" t="n">
         <v>153</v>
@@ -20552,10 +20552,10 @@
         <v>0</v>
       </c>
       <c r="E148" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F148" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G148" t="n">
         <v>153</v>
@@ -20575,10 +20575,10 @@
         <v>0</v>
       </c>
       <c r="E149" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F149" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G149" t="n">
         <v>153</v>
@@ -20598,10 +20598,10 @@
         <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F150" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G150" t="n">
         <v>153</v>
@@ -20621,10 +20621,10 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F151" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G151" t="n">
         <v>153</v>
@@ -20644,10 +20644,10 @@
         <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F152" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G152" t="n">
         <v>153</v>
@@ -20667,10 +20667,10 @@
         <v>0</v>
       </c>
       <c r="E153" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F153" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G153" t="n">
         <v>153</v>
@@ -20690,10 +20690,10 @@
         <v>0</v>
       </c>
       <c r="E154" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F154" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G154" t="n">
         <v>153</v>
@@ -20713,10 +20713,10 @@
         <v>0</v>
       </c>
       <c r="E155" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F155" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G155" t="n">
         <v>153</v>
@@ -20736,10 +20736,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E156" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F156" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G156" t="n">
         <v>153</v>
@@ -20759,10 +20759,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E157" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F157" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G157" t="n">
         <v>153</v>
@@ -20782,10 +20782,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E158" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F158" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G158" t="n">
         <v>153</v>
@@ -20805,10 +20805,10 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F159" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G159" t="n">
         <v>153</v>
@@ -20828,10 +20828,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E160" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F160" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G160" t="n">
         <v>153</v>
@@ -20851,10 +20851,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E161" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F161" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G161" t="n">
         <v>153</v>
@@ -20874,10 +20874,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E162" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F162" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G162" t="n">
         <v>153</v>
@@ -20897,10 +20897,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E163" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F163" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G163" t="n">
         <v>153</v>
@@ -20920,10 +20920,10 @@
         <v>0</v>
       </c>
       <c r="E164" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F164" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G164" t="n">
         <v>153</v>
@@ -20943,10 +20943,10 @@
         <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F165" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G165" t="n">
         <v>153</v>
@@ -20966,10 +20966,10 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F166" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G166" t="n">
         <v>153</v>
@@ -20989,10 +20989,10 @@
         <v>0</v>
       </c>
       <c r="E167" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F167" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G167" t="n">
         <v>153</v>
@@ -21012,10 +21012,10 @@
         <v>0</v>
       </c>
       <c r="E168" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F168" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G168" t="n">
         <v>153</v>
@@ -21035,10 +21035,10 @@
         <v>0</v>
       </c>
       <c r="E169" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F169" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G169" t="n">
         <v>153</v>
@@ -21058,10 +21058,10 @@
         <v>0</v>
       </c>
       <c r="E170" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F170" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G170" t="n">
         <v>153</v>
@@ -21081,10 +21081,10 @@
         <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F171" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G171" t="n">
         <v>153</v>
@@ -21104,10 +21104,10 @@
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F172" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G172" t="n">
         <v>153</v>
@@ -21127,10 +21127,10 @@
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F173" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G173" t="n">
         <v>153</v>
@@ -21150,10 +21150,10 @@
         <v>0</v>
       </c>
       <c r="E174" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F174" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G174" t="n">
         <v>153</v>
@@ -21173,10 +21173,10 @@
         <v>0</v>
       </c>
       <c r="E175" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F175" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G175" t="n">
         <v>153</v>
@@ -21196,10 +21196,10 @@
         <v>0</v>
       </c>
       <c r="E176" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F176" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G176" t="n">
         <v>153</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F177" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G177" t="n">
         <v>153</v>
@@ -21242,10 +21242,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E178" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F178" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G178" t="n">
         <v>153</v>
@@ -21265,10 +21265,10 @@
         <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F179" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G179" t="n">
         <v>153</v>
@@ -21288,10 +21288,10 @@
         <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F180" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G180" t="n">
         <v>153</v>
@@ -21311,10 +21311,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E181" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F181" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G181" t="n">
         <v>153</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F182" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G182" t="n">
         <v>153</v>
@@ -21357,10 +21357,10 @@
         <v>0</v>
       </c>
       <c r="E183" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F183" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G183" t="n">
         <v>153</v>
@@ -21380,10 +21380,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E184" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F184" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G184" t="n">
         <v>153</v>
@@ -21403,10 +21403,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E185" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F185" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G185" t="n">
         <v>153</v>
@@ -21426,10 +21426,10 @@
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F186" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G186" t="n">
         <v>153</v>
@@ -21449,10 +21449,10 @@
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F187" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G187" t="n">
         <v>153</v>
@@ -21472,10 +21472,10 @@
         <v>0</v>
       </c>
       <c r="E188" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F188" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G188" t="n">
         <v>153</v>
@@ -21495,10 +21495,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E189" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F189" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G189" t="n">
         <v>153</v>
@@ -21518,10 +21518,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E190" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F190" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G190" t="n">
         <v>153</v>
@@ -21541,10 +21541,10 @@
         <v>0</v>
       </c>
       <c r="E191" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F191" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G191" t="n">
         <v>153</v>
@@ -21564,10 +21564,10 @@
         <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F192" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G192" t="n">
         <v>153</v>
@@ -21587,10 +21587,10 @@
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F193" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G193" t="n">
         <v>153</v>
@@ -21610,10 +21610,10 @@
         <v>0</v>
       </c>
       <c r="E194" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F194" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G194" t="n">
         <v>153</v>
@@ -21633,10 +21633,10 @@
         <v>0</v>
       </c>
       <c r="E195" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F195" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G195" t="n">
         <v>153</v>
@@ -21656,10 +21656,10 @@
         <v>0</v>
       </c>
       <c r="E196" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F196" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G196" t="n">
         <v>153</v>
@@ -21679,10 +21679,10 @@
         <v>0</v>
       </c>
       <c r="E197" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F197" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G197" t="n">
         <v>153</v>
@@ -21702,10 +21702,10 @@
         <v>0</v>
       </c>
       <c r="E198" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F198" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G198" t="n">
         <v>153</v>
@@ -21725,10 +21725,10 @@
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F199" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G199" t="n">
         <v>153</v>
@@ -21748,10 +21748,10 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F200" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G200" t="n">
         <v>153</v>
@@ -21771,10 +21771,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E201" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F201" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G201" t="n">
         <v>153</v>
@@ -21794,10 +21794,10 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F202" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G202" t="n">
         <v>153</v>
@@ -21817,10 +21817,10 @@
         <v>0</v>
       </c>
       <c r="E203" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F203" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G203" t="n">
         <v>153</v>
@@ -21840,10 +21840,10 @@
         <v>0</v>
       </c>
       <c r="E204" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F204" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G204" t="n">
         <v>153</v>
@@ -21863,10 +21863,10 @@
         <v>0</v>
       </c>
       <c r="E205" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F205" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G205" t="n">
         <v>153</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="E206" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F206" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G206" t="n">
         <v>153</v>
@@ -21909,10 +21909,10 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F207" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G207" t="n">
         <v>153</v>
@@ -21932,10 +21932,10 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F208" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G208" t="n">
         <v>153</v>
@@ -21955,10 +21955,10 @@
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F209" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G209" t="n">
         <v>153</v>
@@ -21978,10 +21978,10 @@
         <v>0</v>
       </c>
       <c r="E210" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F210" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G210" t="n">
         <v>153</v>
@@ -22001,10 +22001,10 @@
         <v>0</v>
       </c>
       <c r="E211" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F211" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G211" t="n">
         <v>153</v>
@@ -22024,10 +22024,10 @@
         <v>0</v>
       </c>
       <c r="E212" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F212" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G212" t="n">
         <v>153</v>
@@ -22047,10 +22047,10 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F213" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G213" t="n">
         <v>153</v>
@@ -22070,10 +22070,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E214" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F214" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G214" t="n">
         <v>153</v>
@@ -22093,10 +22093,10 @@
         <v>0</v>
       </c>
       <c r="E215" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F215" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G215" t="n">
         <v>153</v>
@@ -22116,10 +22116,10 @@
         <v>0</v>
       </c>
       <c r="E216" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F216" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G216" t="n">
         <v>153</v>
@@ -22139,10 +22139,10 @@
         <v>0</v>
       </c>
       <c r="E217" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F217" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G217" t="n">
         <v>153</v>
@@ -22162,10 +22162,10 @@
         <v>0</v>
       </c>
       <c r="E218" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F218" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G218" t="n">
         <v>153</v>
@@ -22185,10 +22185,10 @@
         <v>0</v>
       </c>
       <c r="E219" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F219" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G219" t="n">
         <v>153</v>
@@ -22208,10 +22208,10 @@
         <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F220" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G220" t="n">
         <v>153</v>
@@ -22231,10 +22231,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E221" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F221" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G221" t="n">
         <v>153</v>
@@ -22254,10 +22254,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E222" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F222" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G222" t="n">
         <v>153</v>
@@ -22277,10 +22277,10 @@
         <v>0</v>
       </c>
       <c r="E223" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F223" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G223" t="n">
         <v>153</v>
@@ -22300,10 +22300,10 @@
         <v>0</v>
       </c>
       <c r="E224" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F224" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G224" t="n">
         <v>153</v>
@@ -22323,10 +22323,10 @@
         <v>0</v>
       </c>
       <c r="E225" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F225" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G225" t="n">
         <v>153</v>
@@ -22346,10 +22346,10 @@
         <v>0</v>
       </c>
       <c r="E226" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F226" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G226" t="n">
         <v>153</v>
@@ -22369,10 +22369,10 @@
         <v>0</v>
       </c>
       <c r="E227" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F227" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G227" t="n">
         <v>136</v>
@@ -22392,10 +22392,10 @@
         <v>0</v>
       </c>
       <c r="E228" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F228" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G228" t="n">
         <v>136</v>
@@ -22415,10 +22415,10 @@
         <v>0</v>
       </c>
       <c r="E229" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F229" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G229" t="n">
         <v>136</v>
@@ -22438,10 +22438,10 @@
         <v>0</v>
       </c>
       <c r="E230" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F230" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G230" t="n">
         <v>136</v>
@@ -22461,10 +22461,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E231" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F231" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G231" t="n">
         <v>136</v>
@@ -22484,10 +22484,10 @@
         <v>0</v>
       </c>
       <c r="E232" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F232" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G232" t="n">
         <v>136</v>
@@ -22507,10 +22507,10 @@
         <v>0</v>
       </c>
       <c r="E233" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F233" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G233" t="n">
         <v>136</v>
@@ -22530,10 +22530,10 @@
         <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F234" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G234" t="n">
         <v>136</v>
@@ -22553,10 +22553,10 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F235" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G235" t="n">
         <v>136</v>
@@ -22576,10 +22576,10 @@
         <v>0</v>
       </c>
       <c r="E236" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F236" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G236" t="n">
         <v>136</v>
@@ -22599,10 +22599,10 @@
         <v>0</v>
       </c>
       <c r="E237" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F237" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G237" t="n">
         <v>136</v>
@@ -22622,10 +22622,10 @@
         <v>0</v>
       </c>
       <c r="E238" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F238" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G238" t="n">
         <v>136</v>
@@ -22645,10 +22645,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E239" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F239" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G239" t="n">
         <v>136</v>
@@ -22668,10 +22668,10 @@
         <v>0</v>
       </c>
       <c r="E240" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F240" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G240" t="n">
         <v>136</v>
@@ -22691,10 +22691,10 @@
         <v>0</v>
       </c>
       <c r="E241" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F241" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G241" t="n">
         <v>136</v>
@@ -22714,10 +22714,10 @@
         <v>0</v>
       </c>
       <c r="E242" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F242" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G242" t="n">
         <v>136</v>
@@ -22737,10 +22737,10 @@
         <v>0</v>
       </c>
       <c r="E243" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F243" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G243" t="n">
         <v>136</v>
@@ -22760,10 +22760,10 @@
         <v>0</v>
       </c>
       <c r="E244" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F244" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G244" t="n">
         <v>136</v>
@@ -22783,10 +22783,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E245" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F245" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G245" t="n">
         <v>136</v>
@@ -22806,10 +22806,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E246" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F246" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G246" t="n">
         <v>136</v>
@@ -22829,10 +22829,10 @@
         <v>0</v>
       </c>
       <c r="E247" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F247" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G247" t="n">
         <v>136</v>
@@ -22852,10 +22852,10 @@
         <v>0</v>
       </c>
       <c r="E248" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F248" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G248" t="n">
         <v>136</v>
@@ -22875,10 +22875,10 @@
         <v>0</v>
       </c>
       <c r="E249" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F249" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G249" t="n">
         <v>136</v>
@@ -22898,10 +22898,10 @@
         <v>0.0152284263959391</v>
       </c>
       <c r="E250" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F250" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G250" t="n">
         <v>136</v>
@@ -22921,10 +22921,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E251" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F251" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G251" t="n">
         <v>136</v>
@@ -22944,10 +22944,10 @@
         <v>0</v>
       </c>
       <c r="E252" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F252" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G252" t="n">
         <v>136</v>
@@ -22967,10 +22967,10 @@
         <v>0</v>
       </c>
       <c r="E253" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F253" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G253" t="n">
         <v>136</v>
@@ -22990,10 +22990,10 @@
         <v>0</v>
       </c>
       <c r="E254" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F254" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G254" t="n">
         <v>136</v>
@@ -23013,10 +23013,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E255" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F255" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G255" t="n">
         <v>136</v>
@@ -23036,10 +23036,10 @@
         <v>0</v>
       </c>
       <c r="E256" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F256" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G256" t="n">
         <v>136</v>
@@ -23059,10 +23059,10 @@
         <v>0</v>
       </c>
       <c r="E257" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F257" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G257" t="n">
         <v>136</v>
@@ -23082,10 +23082,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E258" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F258" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G258" t="n">
         <v>136</v>
@@ -23105,10 +23105,10 @@
         <v>0</v>
       </c>
       <c r="E259" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F259" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G259" t="n">
         <v>136</v>
@@ -23128,10 +23128,10 @@
         <v>0</v>
       </c>
       <c r="E260" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F260" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G260" t="n">
         <v>136</v>
@@ -23151,10 +23151,10 @@
         <v>0</v>
       </c>
       <c r="E261" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F261" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G261" t="n">
         <v>136</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="E262" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F262" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G262" t="n">
         <v>136</v>
@@ -23197,10 +23197,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E263" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F263" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G263" t="n">
         <v>136</v>
@@ -23220,10 +23220,10 @@
         <v>0</v>
       </c>
       <c r="E264" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F264" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G264" t="n">
         <v>136</v>
@@ -23243,10 +23243,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E265" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F265" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G265" t="n">
         <v>136</v>
@@ -23266,10 +23266,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E266" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F266" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G266" t="n">
         <v>136</v>
@@ -23289,10 +23289,10 @@
         <v>0</v>
       </c>
       <c r="E267" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F267" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G267" t="n">
         <v>136</v>
@@ -23312,10 +23312,10 @@
         <v>0</v>
       </c>
       <c r="E268" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F268" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G268" t="n">
         <v>136</v>
@@ -23335,10 +23335,10 @@
         <v>0</v>
       </c>
       <c r="E269" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F269" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G269" t="n">
         <v>136</v>
@@ -23358,10 +23358,10 @@
         <v>0</v>
       </c>
       <c r="E270" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F270" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G270" t="n">
         <v>136</v>
@@ -23381,10 +23381,10 @@
         <v>0</v>
       </c>
       <c r="E271" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F271" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G271" t="n">
         <v>136</v>
@@ -23404,10 +23404,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E272" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F272" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G272" t="n">
         <v>136</v>
@@ -23427,10 +23427,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E273" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F273" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G273" t="n">
         <v>136</v>
@@ -23450,10 +23450,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E274" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F274" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G274" t="n">
         <v>136</v>
@@ -23473,10 +23473,10 @@
         <v>0</v>
       </c>
       <c r="E275" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F275" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G275" t="n">
         <v>136</v>
@@ -23496,10 +23496,10 @@
         <v>0</v>
       </c>
       <c r="E276" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F276" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G276" t="n">
         <v>136</v>
@@ -23519,10 +23519,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E277" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F277" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G277" t="n">
         <v>136</v>
@@ -23542,10 +23542,10 @@
         <v>0</v>
       </c>
       <c r="E278" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F278" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G278" t="n">
         <v>136</v>
@@ -23565,10 +23565,10 @@
         <v>0</v>
       </c>
       <c r="E279" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F279" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G279" t="n">
         <v>136</v>
@@ -23588,10 +23588,10 @@
         <v>0</v>
       </c>
       <c r="E280" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F280" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G280" t="n">
         <v>136</v>
@@ -23611,10 +23611,10 @@
         <v>0</v>
       </c>
       <c r="E281" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F281" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G281" t="n">
         <v>136</v>
@@ -23634,10 +23634,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E282" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F282" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G282" t="n">
         <v>136</v>
@@ -23657,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="E283" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F283" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G283" t="n">
         <v>136</v>
@@ -23680,10 +23680,10 @@
         <v>0</v>
       </c>
       <c r="E284" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F284" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G284" t="n">
         <v>136</v>
@@ -23703,10 +23703,10 @@
         <v>0</v>
       </c>
       <c r="E285" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F285" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G285" t="n">
         <v>136</v>
@@ -23726,10 +23726,10 @@
         <v>0</v>
       </c>
       <c r="E286" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F286" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G286" t="n">
         <v>136</v>
@@ -23749,10 +23749,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E287" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F287" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G287" t="n">
         <v>136</v>
@@ -23772,10 +23772,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E288" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F288" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G288" t="n">
         <v>136</v>
@@ -23795,10 +23795,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E289" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F289" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G289" t="n">
         <v>136</v>
@@ -23818,10 +23818,10 @@
         <v>0</v>
       </c>
       <c r="E290" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F290" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G290" t="n">
         <v>136</v>
@@ -23841,10 +23841,10 @@
         <v>0</v>
       </c>
       <c r="E291" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F291" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G291" t="n">
         <v>136</v>
@@ -23864,10 +23864,10 @@
         <v>0</v>
       </c>
       <c r="E292" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F292" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G292" t="n">
         <v>136</v>
@@ -23887,10 +23887,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E293" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F293" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G293" t="n">
         <v>136</v>
@@ -23910,10 +23910,10 @@
         <v>0</v>
       </c>
       <c r="E294" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F294" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G294" t="n">
         <v>136</v>
@@ -23933,10 +23933,10 @@
         <v>0</v>
       </c>
       <c r="E295" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F295" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G295" t="n">
         <v>136</v>
@@ -23956,10 +23956,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E296" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F296" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G296" t="n">
         <v>136</v>
@@ -23979,10 +23979,10 @@
         <v>0</v>
       </c>
       <c r="E297" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F297" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G297" t="n">
         <v>136</v>
@@ -24002,10 +24002,10 @@
         <v>0</v>
       </c>
       <c r="E298" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F298" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G298" t="n">
         <v>136</v>
@@ -24025,10 +24025,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E299" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F299" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G299" t="n">
         <v>136</v>
@@ -24048,10 +24048,10 @@
         <v>0</v>
       </c>
       <c r="E300" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F300" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G300" t="n">
         <v>136</v>
@@ -24071,10 +24071,10 @@
         <v>0</v>
       </c>
       <c r="E301" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F301" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G301" t="n">
         <v>136</v>
@@ -24094,10 +24094,10 @@
         <v>0</v>
       </c>
       <c r="E302" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F302" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G302" t="n">
         <v>136</v>
@@ -24117,10 +24117,10 @@
         <v>0</v>
       </c>
       <c r="E303" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F303" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G303" t="n">
         <v>136</v>
@@ -24140,10 +24140,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E304" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F304" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G304" t="n">
         <v>136</v>
@@ -24163,10 +24163,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E305" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F305" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G305" t="n">
         <v>136</v>
@@ -24186,10 +24186,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E306" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F306" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G306" t="n">
         <v>136</v>
@@ -24209,10 +24209,10 @@
         <v>0</v>
       </c>
       <c r="E307" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F307" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G307" t="n">
         <v>136</v>
@@ -24232,10 +24232,10 @@
         <v>0</v>
       </c>
       <c r="E308" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F308" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G308" t="n">
         <v>136</v>
@@ -24255,10 +24255,10 @@
         <v>0</v>
       </c>
       <c r="E309" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F309" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G309" t="n">
         <v>136</v>
@@ -24278,10 +24278,10 @@
         <v>0</v>
       </c>
       <c r="E310" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F310" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G310" t="n">
         <v>136</v>
@@ -24301,10 +24301,10 @@
         <v>0</v>
       </c>
       <c r="E311" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F311" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G311" t="n">
         <v>136</v>
@@ -24324,10 +24324,10 @@
         <v>0</v>
       </c>
       <c r="E312" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F312" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G312" t="n">
         <v>136</v>
@@ -24347,10 +24347,10 @@
         <v>0</v>
       </c>
       <c r="E313" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F313" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G313" t="n">
         <v>136</v>
@@ -24370,10 +24370,10 @@
         <v>0</v>
       </c>
       <c r="E314" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F314" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G314" t="n">
         <v>136</v>
@@ -24393,10 +24393,10 @@
         <v>0</v>
       </c>
       <c r="E315" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F315" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G315" t="n">
         <v>136</v>
@@ -24416,10 +24416,10 @@
         <v>0</v>
       </c>
       <c r="E316" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F316" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G316" t="n">
         <v>136</v>
@@ -24439,10 +24439,10 @@
         <v>0</v>
       </c>
       <c r="E317" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F317" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G317" t="n">
         <v>136</v>
@@ -24462,10 +24462,10 @@
         <v>0</v>
       </c>
       <c r="E318" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F318" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G318" t="n">
         <v>136</v>
@@ -24485,10 +24485,10 @@
         <v>0</v>
       </c>
       <c r="E319" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F319" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G319" t="n">
         <v>136</v>
@@ -24508,10 +24508,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E320" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F320" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G320" t="n">
         <v>136</v>
@@ -24531,10 +24531,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E321" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F321" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G321" t="n">
         <v>136</v>
@@ -24554,10 +24554,10 @@
         <v>0</v>
       </c>
       <c r="E322" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F322" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G322" t="n">
         <v>136</v>
@@ -24577,10 +24577,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E323" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F323" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G323" t="n">
         <v>136</v>
@@ -24600,10 +24600,10 @@
         <v>0</v>
       </c>
       <c r="E324" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F324" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G324" t="n">
         <v>136</v>
@@ -24623,10 +24623,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E325" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F325" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G325" t="n">
         <v>136</v>
@@ -24646,10 +24646,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E326" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F326" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G326" t="n">
         <v>136</v>
@@ -24669,10 +24669,10 @@
         <v>0</v>
       </c>
       <c r="E327" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F327" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G327" t="n">
         <v>136</v>
@@ -24692,10 +24692,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E328" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F328" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G328" t="n">
         <v>136</v>
@@ -24715,10 +24715,10 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="E329" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F329" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G329" t="n">
         <v>136</v>
@@ -24738,10 +24738,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E330" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F330" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G330" t="n">
         <v>136</v>
@@ -24761,10 +24761,10 @@
         <v>0</v>
       </c>
       <c r="E331" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F331" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G331" t="n">
         <v>136</v>
@@ -24784,10 +24784,10 @@
         <v>0</v>
       </c>
       <c r="E332" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F332" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G332" t="n">
         <v>136</v>
@@ -24807,10 +24807,10 @@
         <v>0</v>
       </c>
       <c r="E333" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F333" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G333" t="n">
         <v>136</v>
@@ -24830,10 +24830,10 @@
         <v>0</v>
       </c>
       <c r="E334" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F334" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G334" t="n">
         <v>136</v>
@@ -24853,10 +24853,10 @@
         <v>0</v>
       </c>
       <c r="E335" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F335" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G335" t="n">
         <v>136</v>
@@ -24876,10 +24876,10 @@
         <v>0</v>
       </c>
       <c r="E336" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F336" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G336" t="n">
         <v>136</v>
@@ -24899,10 +24899,10 @@
         <v>0</v>
       </c>
       <c r="E337" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F337" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G337" t="n">
         <v>136</v>
@@ -24922,10 +24922,10 @@
         <v>0</v>
       </c>
       <c r="E338" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F338" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G338" t="n">
         <v>136</v>
@@ -24945,10 +24945,10 @@
         <v>0</v>
       </c>
       <c r="E339" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F339" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G339" t="n">
         <v>136</v>
@@ -24968,10 +24968,10 @@
         <v>0</v>
       </c>
       <c r="E340" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F340" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G340" t="n">
         <v>136</v>
@@ -24991,10 +24991,10 @@
         <v>0</v>
       </c>
       <c r="E341" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F341" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G341" t="n">
         <v>136</v>
@@ -25014,10 +25014,10 @@
         <v>0</v>
       </c>
       <c r="E342" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F342" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G342" t="n">
         <v>136</v>
@@ -25037,10 +25037,10 @@
         <v>0</v>
       </c>
       <c r="E343" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F343" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G343" t="n">
         <v>136</v>
@@ -25060,10 +25060,10 @@
         <v>0</v>
       </c>
       <c r="E344" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F344" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G344" t="n">
         <v>136</v>
@@ -25083,10 +25083,10 @@
         <v>0</v>
       </c>
       <c r="E345" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F345" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G345" t="n">
         <v>136</v>
@@ -25106,10 +25106,10 @@
         <v>0.0050251256281407</v>
       </c>
       <c r="E346" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F346" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G346" t="n">
         <v>136</v>
@@ -25129,10 +25129,10 @@
         <v>0</v>
       </c>
       <c r="E347" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F347" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G347" t="n">
         <v>136</v>
@@ -25152,10 +25152,10 @@
         <v>0</v>
       </c>
       <c r="E348" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F348" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G348" t="n">
         <v>136</v>
@@ -25175,10 +25175,10 @@
         <v>0</v>
       </c>
       <c r="E349" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F349" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G349" t="n">
         <v>136</v>
@@ -25198,10 +25198,10 @@
         <v>0</v>
       </c>
       <c r="E350" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F350" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G350" t="n">
         <v>136</v>
@@ -25221,10 +25221,10 @@
         <v>0</v>
       </c>
       <c r="E351" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F351" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G351" t="n">
         <v>136</v>
@@ -25244,10 +25244,10 @@
         <v>0</v>
       </c>
       <c r="E352" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F352" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G352" t="n">
         <v>136</v>
@@ -25267,10 +25267,10 @@
         <v>0</v>
       </c>
       <c r="E353" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F353" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G353" t="n">
         <v>136</v>
@@ -25290,10 +25290,10 @@
         <v>0</v>
       </c>
       <c r="E354" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F354" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G354" t="n">
         <v>136</v>
@@ -25313,10 +25313,10 @@
         <v>0</v>
       </c>
       <c r="E355" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F355" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G355" t="n">
         <v>136</v>
@@ -25336,10 +25336,10 @@
         <v>0</v>
       </c>
       <c r="E356" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F356" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G356" t="n">
         <v>136</v>
@@ -25359,10 +25359,10 @@
         <v>0</v>
       </c>
       <c r="E357" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F357" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G357" t="n">
         <v>136</v>
@@ -25382,10 +25382,10 @@
         <v>0</v>
       </c>
       <c r="E358" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F358" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G358" t="n">
         <v>136</v>
@@ -25405,10 +25405,10 @@
         <v>0</v>
       </c>
       <c r="E359" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F359" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G359" t="n">
         <v>136</v>
@@ -25428,10 +25428,10 @@
         <v>0</v>
       </c>
       <c r="E360" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F360" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G360" t="n">
         <v>136</v>
@@ -25451,10 +25451,10 @@
         <v>0</v>
       </c>
       <c r="E361" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F361" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G361" t="n">
         <v>136</v>
@@ -25474,10 +25474,10 @@
         <v>0</v>
       </c>
       <c r="E362" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F362" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G362" t="n">
         <v>136</v>
